--- a/database/event/6477/event_6477_evp_summary.xlsx
+++ b/database/event/6477/event_6477_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.0863</v>
+        <v>5.0536</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5572</v>
+        <v>0.5536</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6334</v>
+        <v>1.5694</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0863</v>
+        <v>5.0536</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3995</v>
+        <v>4.3668</v>
       </c>
       <c r="G2" t="n">
         <v>0.6868</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5953</v>
+        <v>4.5441</v>
       </c>
       <c r="I2" t="n">
         <v>4.6598</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.9071</v>
+        <v>4.9746</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5376</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>1.561</v>
+        <v>1.538</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9071</v>
+        <v>4.9746</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9132</v>
+        <v>4.8429</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9939</v>
+        <v>0.1317</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9132</v>
+        <v>5.2907</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9541</v>
+        <v>5.2907</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9939</v>
+        <v>0.1317</v>
       </c>
       <c r="K3" t="n">
-        <v>262</v>
+        <v>155</v>
       </c>
       <c r="L3" t="n">
         <v>52</v>
       </c>
       <c r="M3" t="n">
-        <v>4.948</v>
+        <v>5.422400000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>314</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3817</v>
+        <v>4.8746</v>
       </c>
       <c r="C4" t="n">
-        <v>0.48</v>
+        <v>0.534</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3487</v>
+        <v>1.4981</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3817</v>
+        <v>4.8746</v>
       </c>
       <c r="F4" t="n">
-        <v>4.25</v>
+        <v>2.8807</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1317</v>
+        <v>1.9939</v>
       </c>
       <c r="H4" t="n">
-        <v>4.361</v>
+        <v>2.8807</v>
       </c>
       <c r="I4" t="n">
-        <v>4.361</v>
+        <v>2.9541</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1317</v>
+        <v>1.9939</v>
       </c>
       <c r="K4" t="n">
-        <v>155</v>
+        <v>262</v>
       </c>
       <c r="L4" t="n">
         <v>52</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4927</v>
+        <v>4.948</v>
       </c>
       <c r="N4" t="n">
-        <v>207</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5">
@@ -640,7 +640,7 @@
         <v>0.3895</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0152</v>
+        <v>0.9728</v>
       </c>
       <c r="E5" t="n">
         <v>3.556</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.7191</v>
+        <v>2.683</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2979</v>
+        <v>0.2939</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6771</v>
+        <v>0.625</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7191</v>
+        <v>2.683</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2387</v>
+        <v>3.2026</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5196</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2387</v>
+        <v>3.2026</v>
       </c>
       <c r="I6" t="n">
         <v>3.2842</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.6815</v>
+        <v>2.6665</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2937</v>
+        <v>0.2921</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6619</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6815</v>
+        <v>2.6665</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3432</v>
+        <v>1.3282</v>
       </c>
       <c r="G7" t="n">
         <v>1.3383</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3432</v>
+        <v>1.3282</v>
       </c>
       <c r="I7" t="n">
         <v>1.362</v>
@@ -778,7 +778,7 @@
         <v>0.2653</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5571</v>
+        <v>0.5211</v>
       </c>
       <c r="E8" t="n">
         <v>2.4221</v>
@@ -824,7 +824,7 @@
         <v>0.2502</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5013</v>
+        <v>0.466</v>
       </c>
       <c r="E9" t="n">
         <v>2.2839</v>
@@ -870,7 +870,7 @@
         <v>0.2459</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4853</v>
+        <v>0.4502</v>
       </c>
       <c r="E10" t="n">
         <v>2.2443</v>
@@ -916,7 +916,7 @@
         <v>0.2045</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3329</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="n">
         <v>1.8672</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.635</v>
+        <v>1.7245</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1791</v>
+        <v>0.1889</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2391</v>
+        <v>0.2431</v>
       </c>
       <c r="E12" t="n">
-        <v>1.635</v>
+        <v>1.7245</v>
       </c>
       <c r="F12" t="n">
-        <v>1.635</v>
+        <v>1.4863</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.2382</v>
       </c>
       <c r="H12" t="n">
-        <v>1.635</v>
+        <v>1.4863</v>
       </c>
       <c r="I12" t="n">
-        <v>1.635</v>
+        <v>1.4863</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.2382</v>
       </c>
       <c r="K12" t="n">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>1.635</v>
+        <v>1.7245</v>
       </c>
       <c r="N12" t="n">
-        <v>69</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4867</v>
+        <v>1.635</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1629</v>
+        <v>0.1791</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1792</v>
+        <v>0.2075</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4867</v>
+        <v>1.635</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2485</v>
+        <v>1.635</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2382</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2485</v>
+        <v>1.635</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2485</v>
+        <v>1.635</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2382</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="L13" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4867</v>
+        <v>1.635</v>
       </c>
       <c r="N13" t="n">
-        <v>207</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -1054,7 +1054,7 @@
         <v>0.1578</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1604</v>
+        <v>0.1299</v>
       </c>
       <c r="E14" t="n">
         <v>1.4402</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.0003</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1096</v>
+        <v>0.1084</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0173</v>
+        <v>-0.0497</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0003</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.979</v>
+        <v>0.9681</v>
       </c>
       <c r="G15" t="n">
         <v>0.0213</v>
       </c>
       <c r="H15" t="n">
-        <v>0.979</v>
+        <v>0.9681</v>
       </c>
       <c r="I15" t="n">
         <v>0.9927</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9403</v>
+        <v>0.9469</v>
       </c>
       <c r="C16" t="n">
-        <v>0.103</v>
+        <v>0.1037</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0415</v>
+        <v>-0.0667</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9403</v>
+        <v>0.9469</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9403</v>
+        <v>0.9469</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9403</v>
+        <v>0.9469</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9403</v>
+        <v>0.9469</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9403</v>
+        <v>0.9469</v>
       </c>
       <c r="N16" t="n">
         <v>165</v>
@@ -1192,7 +1192,7 @@
         <v>0.1007</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.05</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="E17" t="n">
         <v>0.9192</v>
@@ -1238,7 +1238,7 @@
         <v>0.0924</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0804</v>
+        <v>-0.1077</v>
       </c>
       <c r="E18" t="n">
         <v>0.8439</v>
@@ -1274,185 +1274,185 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4369</v>
+        <v>0.7358</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0479</v>
+        <v>0.0806</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2449</v>
+        <v>-0.1508</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4369</v>
+        <v>0.7358</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4369</v>
+        <v>0.7358</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4369</v>
+        <v>0.7358</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4369</v>
+        <v>0.7358</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>99</v>
+        <v>211</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4369</v>
+        <v>0.7358</v>
       </c>
       <c r="N19" t="n">
-        <v>99</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3965</v>
+        <v>0.7216</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0434</v>
+        <v>0.079</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2612</v>
+        <v>-0.1564</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3965</v>
+        <v>0.7216</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3965</v>
+        <v>0.7216</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3965</v>
+        <v>0.7216</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3965</v>
+        <v>0.7216</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>211</v>
+        <v>99</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3965</v>
+        <v>0.7216</v>
       </c>
       <c r="N20" t="n">
-        <v>211</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3598</v>
+        <v>0.3965</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0394</v>
+        <v>0.0434</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.276</v>
+        <v>-0.2859</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3598</v>
+        <v>0.3965</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3598</v>
+        <v>0.3965</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3598</v>
+        <v>0.3965</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3598</v>
+        <v>0.3965</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3598</v>
+        <v>0.3965</v>
       </c>
       <c r="N21" t="n">
-        <v>159</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1915</v>
+        <v>0.3598</v>
       </c>
       <c r="C22" t="n">
-        <v>0.021</v>
+        <v>0.0394</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.344</v>
+        <v>-0.3006</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1915</v>
+        <v>0.3598</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1915</v>
+        <v>0.3598</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1915</v>
+        <v>0.3598</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1915</v>
+        <v>0.3598</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>211</v>
+        <v>159</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1915</v>
+        <v>0.3598</v>
       </c>
       <c r="N22" t="n">
-        <v>211</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23">
@@ -1468,7 +1468,7 @@
         <v>-0.0028</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4316</v>
+        <v>-0.454</v>
       </c>
       <c r="E23" t="n">
         <v>-0.0254</v>
@@ -1504,139 +1504,139 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Farlig</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2683</v>
+        <v>-0.0579</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0294</v>
+        <v>-0.0063</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.467</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2683</v>
+        <v>-0.0579</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7317</v>
+        <v>-0.0579</v>
       </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7317</v>
+        <v>-0.0579</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7317</v>
+        <v>-0.0579</v>
       </c>
       <c r="J24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="L24" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2683</v>
+        <v>-0.0579</v>
       </c>
       <c r="N24" t="n">
-        <v>207</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kreaz</t>
+          <t>Farlig</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.4038</v>
+        <v>-0.2683</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0442</v>
+        <v>-0.0294</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5845</v>
+        <v>-0.5508</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4038</v>
+        <v>-0.2683</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4038</v>
+        <v>0.7317</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4038</v>
+        <v>0.7317</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4038</v>
+        <v>0.7317</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K25" t="n">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4038</v>
+        <v>-0.2683</v>
       </c>
       <c r="N25" t="n">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>kreaz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.4855</v>
+        <v>-0.4038</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0532</v>
+        <v>-0.0442</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6175</v>
+        <v>-0.6048</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4855</v>
+        <v>-0.4038</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4855</v>
+        <v>-0.4038</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4855</v>
+        <v>-0.4038</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4855</v>
+        <v>-0.4038</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.4855</v>
+        <v>-0.4038</v>
       </c>
       <c r="N26" t="n">
-        <v>159</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27">
@@ -1652,7 +1652,7 @@
         <v>-0.07489999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6975</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="E27" t="n">
         <v>-0.6835</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0769</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7049</v>
+        <v>-0.7235</v>
       </c>
       <c r="E28" t="n">
         <v>-0.7019</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0804</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.718</v>
+        <v>-0.7365</v>
       </c>
       <c r="E29" t="n">
         <v>-0.7343</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0863</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7398</v>
+        <v>-0.7579</v>
       </c>
       <c r="E30" t="n">
         <v>-0.7882</v>
@@ -1836,7 +1836,7 @@
         <v>-0.09909999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7869</v>
+        <v>-0.8044</v>
       </c>
       <c r="E31" t="n">
         <v>-0.9049</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1046</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8069</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="E32" t="n">
         <v>-0.9544</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1187</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.859</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="E33" t="n">
         <v>-1.0832</v>
@@ -1974,7 +1974,7 @@
         <v>-0.139</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.9495</v>
       </c>
       <c r="E34" t="n">
         <v>-1.269</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1396</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9361</v>
+        <v>-0.9516</v>
       </c>
       <c r="E35" t="n">
         <v>-1.2742</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1456</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9584</v>
+        <v>-0.9735</v>
       </c>
       <c r="E36" t="n">
         <v>-1.3294</v>
@@ -2112,7 +2112,7 @@
         <v>-0.1503</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9757</v>
+        <v>-0.9906</v>
       </c>
       <c r="E37" t="n">
         <v>-1.3721</v>
@@ -2158,7 +2158,7 @@
         <v>-0.1538</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9886</v>
+        <v>-1.0033</v>
       </c>
       <c r="E38" t="n">
         <v>-1.4042</v>
@@ -2204,7 +2204,7 @@
         <v>-0.1664</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0351</v>
+        <v>-1.0492</v>
       </c>
       <c r="E39" t="n">
         <v>-1.5193</v>
@@ -2250,7 +2250,7 @@
         <v>-0.1868</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1101</v>
+        <v>-1.1231</v>
       </c>
       <c r="E40" t="n">
         <v>-1.7049</v>
@@ -2296,7 +2296,7 @@
         <v>-0.1905</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1238</v>
+        <v>-1.1366</v>
       </c>
       <c r="E41" t="n">
         <v>-1.7388</v>
@@ -2342,7 +2342,7 @@
         <v>-0.2542</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.3589</v>
+        <v>-1.3685</v>
       </c>
       <c r="E42" t="n">
         <v>-2.3207</v>

--- a/database/event/6477/event_6477_evp_summary.xlsx
+++ b/database/event/6477/event_6477_evp_summary.xlsx
@@ -492,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.0536</v>
+        <v>4.9612</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5536</v>
+        <v>0.5435</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5694</v>
+        <v>1.6017</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0536</v>
+        <v>4.9612</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3668</v>
+        <v>4.6616</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6868</v>
+        <v>0.2996</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5441</v>
+        <v>6.8761</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6598</v>
+        <v>6.8761</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6868</v>
+        <v>0.2996</v>
       </c>
       <c r="K2" t="n">
-        <v>262</v>
+        <v>155</v>
       </c>
       <c r="L2" t="n">
         <v>52</v>
       </c>
       <c r="M2" t="n">
-        <v>5.3466</v>
+        <v>7.1757</v>
       </c>
       <c r="N2" t="n">
-        <v>314</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.9746</v>
+        <v>4.7371</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.5189</v>
       </c>
       <c r="D3" t="n">
-        <v>1.538</v>
+        <v>1.5006</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9746</v>
+        <v>4.7371</v>
       </c>
       <c r="F3" t="n">
-        <v>4.8429</v>
+        <v>4.1127</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1317</v>
+        <v>0.6244</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2907</v>
+        <v>5.6709</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2907</v>
+        <v>6.3997</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1317</v>
+        <v>0.6244</v>
       </c>
       <c r="K3" t="n">
-        <v>155</v>
+        <v>262</v>
       </c>
       <c r="L3" t="n">
         <v>52</v>
       </c>
       <c r="M3" t="n">
-        <v>5.422400000000001</v>
+        <v>7.0241</v>
       </c>
       <c r="N3" t="n">
-        <v>207</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4">
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8746</v>
+        <v>4.4135</v>
       </c>
       <c r="C4" t="n">
-        <v>0.534</v>
+        <v>0.4835</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4981</v>
+        <v>1.3545</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8746</v>
+        <v>4.4135</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8807</v>
+        <v>2.4703</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9939</v>
+        <v>1.9432</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8807</v>
+        <v>2.4703</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9541</v>
+        <v>2.7878</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9939</v>
+        <v>1.9432</v>
       </c>
       <c r="K4" t="n">
         <v>262</v>
@@ -621,7 +621,7 @@
         <v>52</v>
       </c>
       <c r="M4" t="n">
-        <v>4.948</v>
+        <v>4.731</v>
       </c>
       <c r="N4" t="n">
         <v>314</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.556</v>
+        <v>3.5934</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3895</v>
+        <v>0.3936</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9728</v>
+        <v>0.9842</v>
       </c>
       <c r="E5" t="n">
-        <v>3.556</v>
+        <v>3.5934</v>
       </c>
       <c r="F5" t="n">
-        <v>3.556</v>
+        <v>3.5934</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.556</v>
+        <v>4.5306</v>
       </c>
       <c r="I5" t="n">
-        <v>3.556</v>
+        <v>4.5306</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.556</v>
+        <v>4.5306</v>
       </c>
       <c r="N5" t="n">
         <v>194</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.683</v>
+        <v>3.2809</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2939</v>
+        <v>0.3594</v>
       </c>
       <c r="D6" t="n">
-        <v>0.625</v>
+        <v>0.8431</v>
       </c>
       <c r="E6" t="n">
-        <v>2.683</v>
+        <v>3.2809</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2026</v>
+        <v>1.9284</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5196</v>
+        <v>1.3525</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2026</v>
+        <v>1.9284</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2842</v>
+        <v>2.1763</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5196</v>
+        <v>1.3525</v>
       </c>
       <c r="K6" t="n">
         <v>262</v>
@@ -713,7 +713,7 @@
         <v>52</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7646</v>
+        <v>3.5288</v>
       </c>
       <c r="N6" t="n">
         <v>314</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.6665</v>
+        <v>2.7419</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2921</v>
+        <v>0.3004</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.5998</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6665</v>
+        <v>2.7419</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3282</v>
+        <v>2.7419</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3383</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3282</v>
+        <v>2.7419</v>
       </c>
       <c r="I7" t="n">
-        <v>1.362</v>
+        <v>2.7419</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3383</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>262</v>
+        <v>211</v>
       </c>
       <c r="L7" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7003</v>
+        <v>2.7419</v>
       </c>
       <c r="N7" t="n">
-        <v>314</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>PlesseN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4221</v>
+        <v>2.7146</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2653</v>
+        <v>0.2974</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5211</v>
+        <v>0.5875</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4221</v>
+        <v>2.7146</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4221</v>
+        <v>2.7146</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4221</v>
+        <v>2.7146</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4221</v>
+        <v>2.7146</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4221</v>
+        <v>2.7146</v>
       </c>
       <c r="N8" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2839</v>
+        <v>2.5997</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2502</v>
+        <v>0.2848</v>
       </c>
       <c r="D9" t="n">
-        <v>0.466</v>
+        <v>0.5356</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2839</v>
+        <v>2.5997</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2839</v>
+        <v>2.5997</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2839</v>
+        <v>2.5997</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2839</v>
+        <v>2.5997</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2839</v>
+        <v>2.5997</v>
       </c>
       <c r="N9" t="n">
         <v>159</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PlesseN</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2443</v>
+        <v>2.5993</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2459</v>
+        <v>0.2847</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4502</v>
+        <v>0.5354</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2443</v>
+        <v>2.5993</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2443</v>
+        <v>2.9697</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.3704</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2443</v>
+        <v>3.1611</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2443</v>
+        <v>3.5674</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.3704</v>
       </c>
       <c r="K10" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2443</v>
+        <v>3.197</v>
       </c>
       <c r="N10" t="n">
-        <v>194</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8672</v>
+        <v>2.2567</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2045</v>
+        <v>0.2472</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3</v>
+        <v>0.3808</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8672</v>
+        <v>2.2567</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8672</v>
+        <v>2.2567</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8672</v>
+        <v>2.2567</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8672</v>
+        <v>2.2567</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8672</v>
+        <v>2.2567</v>
       </c>
       <c r="N11" t="n">
         <v>194</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7245</v>
+        <v>2.007</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1889</v>
+        <v>0.2199</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2431</v>
+        <v>0.268</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7245</v>
+        <v>2.007</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4863</v>
+        <v>1.795</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2382</v>
+        <v>0.212</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4863</v>
+        <v>1.795</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4863</v>
+        <v>1.795</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2382</v>
+        <v>0.212</v>
       </c>
       <c r="K12" t="n">
         <v>155</v>
@@ -989,7 +989,7 @@
         <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7245</v>
+        <v>2.007</v>
       </c>
       <c r="N12" t="n">
         <v>207</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.635</v>
+        <v>1.879</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1791</v>
+        <v>0.2058</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2075</v>
+        <v>0.2103</v>
       </c>
       <c r="E13" t="n">
-        <v>1.635</v>
+        <v>1.879</v>
       </c>
       <c r="F13" t="n">
-        <v>1.635</v>
+        <v>1.879</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.635</v>
+        <v>1.879</v>
       </c>
       <c r="I13" t="n">
-        <v>1.635</v>
+        <v>1.879</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.635</v>
+        <v>1.879</v>
       </c>
       <c r="N13" t="n">
         <v>69</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4402</v>
+        <v>1.4608</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1578</v>
+        <v>0.16</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1299</v>
+        <v>0.0215</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4402</v>
+        <v>1.4608</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4402</v>
+        <v>1.4608</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4402</v>
+        <v>1.4608</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4402</v>
+        <v>1.4608</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4402</v>
+        <v>1.4608</v>
       </c>
       <c r="N14" t="n">
         <v>165</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9893999999999999</v>
+        <v>1.4149</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1084</v>
+        <v>0.155</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0497</v>
+        <v>0.0007</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9893999999999999</v>
+        <v>1.4149</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9681</v>
+        <v>1.2723</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0213</v>
+        <v>0.1426</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9681</v>
+        <v>1.2723</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9927</v>
+        <v>1.4358</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0213</v>
+        <v>0.1426</v>
       </c>
       <c r="K15" t="n">
         <v>262</v>
@@ -1127,7 +1127,7 @@
         <v>52</v>
       </c>
       <c r="M15" t="n">
-        <v>1.014</v>
+        <v>1.5784</v>
       </c>
       <c r="N15" t="n">
         <v>314</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9469</v>
+        <v>1.2344</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1037</v>
+        <v>0.1352</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0667</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9469</v>
+        <v>1.2344</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9469</v>
+        <v>1.2344</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9469</v>
+        <v>1.2344</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9469</v>
+        <v>1.2344</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9469</v>
+        <v>1.2344</v>
       </c>
       <c r="N16" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9192</v>
+        <v>1.1687</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1007</v>
+        <v>0.128</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.1104</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9192</v>
+        <v>1.1687</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9192</v>
+        <v>1.1687</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9192</v>
+        <v>1.1687</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9192</v>
+        <v>1.1687</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9192</v>
+        <v>1.1687</v>
       </c>
       <c r="N17" t="n">
-        <v>159</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8439</v>
+        <v>1.168</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0924</v>
+        <v>0.1279</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1077</v>
+        <v>-0.1107</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8439</v>
+        <v>1.168</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8439</v>
+        <v>1.168</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8439</v>
+        <v>1.168</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8439</v>
+        <v>1.168</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8439</v>
+        <v>1.168</v>
       </c>
       <c r="N18" t="n">
         <v>165</v>
@@ -1274,47 +1274,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7358</v>
+        <v>1.1235</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0806</v>
+        <v>0.1231</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1508</v>
+        <v>-0.1308</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7358</v>
+        <v>1.1235</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7358</v>
+        <v>1.1235</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7358</v>
+        <v>1.1235</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7358</v>
+        <v>1.1235</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7358</v>
+        <v>1.1235</v>
       </c>
       <c r="N19" t="n">
-        <v>211</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7216</v>
+        <v>0.9156</v>
       </c>
       <c r="C20" t="n">
-        <v>0.079</v>
+        <v>0.1003</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1564</v>
+        <v>-0.2247</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7216</v>
+        <v>0.9156</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7216</v>
+        <v>0.9156</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7216</v>
+        <v>0.9156</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7216</v>
+        <v>0.9156</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7216</v>
+        <v>0.9156</v>
       </c>
       <c r="N20" t="n">
         <v>99</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3965</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0434</v>
+        <v>0.0772</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2859</v>
+        <v>-0.3197</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3965</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3965</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3965</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3965</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3965</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>211</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3598</v>
+        <v>0.6853</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0394</v>
+        <v>0.0751</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3006</v>
+        <v>-0.3286</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3598</v>
+        <v>0.6853</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3598</v>
+        <v>0.6853</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3598</v>
+        <v>0.6853</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3598</v>
+        <v>0.6853</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3598</v>
+        <v>0.6853</v>
       </c>
       <c r="N22" t="n">
         <v>159</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0254</v>
+        <v>0.4528</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0028</v>
+        <v>0.0496</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.454</v>
+        <v>-0.4336</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0254</v>
+        <v>0.4528</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0254</v>
+        <v>0.4528</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0254</v>
+        <v>0.4528</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0254</v>
+        <v>0.4528</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0254</v>
+        <v>0.4528</v>
       </c>
       <c r="N23" t="n">
         <v>71</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Farlig</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0579</v>
+        <v>0.3862</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0063</v>
+        <v>0.0423</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.467</v>
+        <v>-0.4637</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0579</v>
+        <v>0.3862</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0579</v>
+        <v>1.1066</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.7204</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0579</v>
+        <v>1.1066</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0579</v>
+        <v>1.1066</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.7204</v>
       </c>
       <c r="K24" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0579</v>
+        <v>0.3862</v>
       </c>
       <c r="N24" t="n">
-        <v>159</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Farlig</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.2683</v>
+        <v>0.2516</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0294</v>
+        <v>0.0276</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5508</v>
+        <v>-0.5244</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2683</v>
+        <v>0.2516</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7317</v>
+        <v>0.2516</v>
       </c>
       <c r="G25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7317</v>
+        <v>0.2516</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7317</v>
+        <v>0.2516</v>
       </c>
       <c r="J25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="L25" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2683</v>
+        <v>0.2516</v>
       </c>
       <c r="N25" t="n">
-        <v>207</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.4038</v>
+        <v>0.1261</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0442</v>
+        <v>0.0138</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6048</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4038</v>
+        <v>0.1261</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4038</v>
+        <v>0.1261</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4038</v>
+        <v>0.1261</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4038</v>
+        <v>0.1261</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.4038</v>
+        <v>0.1261</v>
       </c>
       <c r="N26" t="n">
         <v>194</v>
@@ -1642,81 +1642,81 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.6835</v>
+        <v>-0.0934</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.0102</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.6802</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6835</v>
+        <v>-0.0934</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6835</v>
+        <v>-1.0274</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.6835</v>
+        <v>-1.0274</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6835</v>
+        <v>-1.0274</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.6835</v>
+        <v>-0.09340000000000004</v>
       </c>
       <c r="N27" t="n">
-        <v>112</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.7019</v>
+        <v>-0.2334</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0769</v>
+        <v>-0.0256</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7235</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.7019</v>
+        <v>-0.2334</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.5088</v>
+        <v>0.3561</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8069</v>
+        <v>-0.5895</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.5088</v>
+        <v>0.3561</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.5088</v>
+        <v>0.3561</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8069</v>
+        <v>-0.5895</v>
       </c>
       <c r="K28" t="n">
         <v>155</v>
@@ -1725,7 +1725,7 @@
         <v>52</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.7019</v>
+        <v>-0.2334</v>
       </c>
       <c r="N28" t="n">
         <v>207</v>
@@ -1734,47 +1734,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>viz</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.7343</v>
+        <v>-0.2607</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0804</v>
+        <v>-0.0286</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7365</v>
+        <v>-0.7557</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.7343</v>
+        <v>-0.2607</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.7343</v>
+        <v>-0.2607</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7343</v>
+        <v>-0.2607</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7343</v>
+        <v>-0.2607</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>71</v>
+        <v>194</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.7343</v>
+        <v>-0.2607</v>
       </c>
       <c r="N29" t="n">
-        <v>71</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7882</v>
+        <v>-0.35</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0863</v>
+        <v>-0.0383</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7579</v>
+        <v>-0.796</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7882</v>
+        <v>-0.35</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7882</v>
+        <v>-0.35</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7882</v>
+        <v>-0.35</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7882</v>
+        <v>-0.35</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7882</v>
+        <v>-0.35</v>
       </c>
       <c r="N30" t="n">
         <v>71</v>
@@ -1826,78 +1826,78 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.9049</v>
+        <v>-0.3582</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.0392</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8044</v>
+        <v>-0.7997</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.9049</v>
+        <v>-0.3582</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0132</v>
+        <v>-0.3582</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.9181</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0132</v>
+        <v>-0.3582</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0132</v>
+        <v>-0.3582</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.9181</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="L31" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.9049</v>
+        <v>-0.3582</v>
       </c>
       <c r="N31" t="n">
-        <v>207</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>djay</t>
+          <t>viz</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.9544</v>
+        <v>-0.5607</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1046</v>
+        <v>-0.0614</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.8911</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9544</v>
+        <v>-0.5607</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9544</v>
+        <v>-0.5607</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.9544</v>
+        <v>-0.5607</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.9544</v>
+        <v>-0.5607</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.9544</v>
+        <v>-0.5607</v>
       </c>
       <c r="N32" t="n">
         <v>71</v>
@@ -1918,231 +1918,231 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0832</v>
+        <v>-0.6388</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1187</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.9264</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0832</v>
+        <v>-0.6388</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.0832</v>
+        <v>-0.6388</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.0832</v>
+        <v>-0.6388</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.0832</v>
+        <v>-0.6388</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.0832</v>
+        <v>-0.6388</v>
       </c>
       <c r="N33" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.269</v>
+        <v>-0.6855</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.139</v>
+        <v>-0.0751</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9495</v>
+        <v>-0.9475</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.269</v>
+        <v>-0.6855</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.269</v>
+        <v>-0.6855</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.269</v>
+        <v>-0.6855</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.269</v>
+        <v>-0.6855</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.269</v>
+        <v>-0.6855</v>
       </c>
       <c r="N34" t="n">
-        <v>69</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tuurtle</t>
+          <t>djay</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.2742</v>
+        <v>-0.7097</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1396</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9516</v>
+        <v>-0.9584</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.2742</v>
+        <v>-0.7097</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.2742</v>
+        <v>-0.7097</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.2742</v>
+        <v>-0.7097</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.2742</v>
+        <v>-0.7097</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2742</v>
+        <v>-0.7097</v>
       </c>
       <c r="N35" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3294</v>
+        <v>-0.8429</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1456</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9735</v>
+        <v>-1.0185</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3294</v>
+        <v>-0.8429</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3294</v>
+        <v>-0.8429</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3294</v>
+        <v>-0.8429</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.3294</v>
+        <v>-0.8429</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.3294</v>
+        <v>-0.8429</v>
       </c>
       <c r="N36" t="n">
-        <v>165</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3721</v>
+        <v>-0.9044</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1503</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9906</v>
+        <v>-1.0463</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3721</v>
+        <v>-0.9044</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.3721</v>
+        <v>-0.9044</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3721</v>
+        <v>-0.9044</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.3721</v>
+        <v>-0.9044</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3721</v>
+        <v>-0.9044</v>
       </c>
       <c r="N37" t="n">
-        <v>211</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4042</v>
+        <v>-0.9308</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1538</v>
+        <v>-0.102</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0033</v>
+        <v>-1.0582</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4042</v>
+        <v>-0.9308</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4042</v>
+        <v>-0.9308</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4042</v>
+        <v>-0.9308</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.4042</v>
+        <v>-0.9308</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4042</v>
+        <v>-0.9308</v>
       </c>
       <c r="N38" t="n">
         <v>69</v>
@@ -2194,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Tuurtle</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5193</v>
+        <v>-1.0695</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1664</v>
+        <v>-0.1172</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0492</v>
+        <v>-1.1208</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5193</v>
+        <v>-1.0695</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5193</v>
+        <v>-1.0695</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5193</v>
+        <v>-1.0695</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5193</v>
+        <v>-1.0695</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5193</v>
+        <v>-1.0695</v>
       </c>
       <c r="N39" t="n">
-        <v>165</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7049</v>
+        <v>-1.1439</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1868</v>
+        <v>-0.1253</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1231</v>
+        <v>-1.1544</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7049</v>
+        <v>-1.1439</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7049</v>
+        <v>-1.1439</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7049</v>
+        <v>-1.1439</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7049</v>
+        <v>-1.1439</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7049</v>
+        <v>-1.1439</v>
       </c>
       <c r="N40" t="n">
         <v>69</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.7388</v>
+        <v>-1.4341</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1905</v>
+        <v>-0.1571</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1366</v>
+        <v>-1.2854</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.7388</v>
+        <v>-1.4341</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.7388</v>
+        <v>-1.4341</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.7388</v>
+        <v>-1.4341</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.7388</v>
+        <v>-1.4341</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.7388</v>
+        <v>-1.4341</v>
       </c>
       <c r="N41" t="n">
         <v>71</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.3207</v>
+        <v>-1.6511</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.2542</v>
+        <v>-0.1809</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.3685</v>
+        <v>-1.3834</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.3207</v>
+        <v>-1.6511</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.3207</v>
+        <v>-1.6511</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.3207</v>
+        <v>-1.6511</v>
       </c>
       <c r="I42" t="n">
-        <v>-2.3207</v>
+        <v>-1.6511</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.3207</v>
+        <v>-1.6511</v>
       </c>
       <c r="N42" t="n">
         <v>159</v>
@@ -2475,10 +2475,10 @@
         <v>1.35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6078</v>
+        <v>0.7343</v>
       </c>
       <c r="J2" t="n">
-        <v>15.195</v>
+        <v>18.3575</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0391</v>
+        <v>0.0123</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9775</v>
+        <v>0.3075</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2881</v>
+        <v>-0.18</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.2025</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.76</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4241</v>
+        <v>-0.2704</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.6025</v>
+        <v>-6.76</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5067</v>
+        <v>-0.3282</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.6675</v>
+        <v>-8.205</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1161</v>
+        <v>1.0714</v>
       </c>
       <c r="J7" t="n">
-        <v>27.9025</v>
+        <v>26.785</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.44</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1161</v>
+        <v>1.0714</v>
       </c>
       <c r="J8" t="n">
-        <v>27.9025</v>
+        <v>26.785</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3712</v>
+        <v>0.4176</v>
       </c>
       <c r="J9" t="n">
-        <v>9.279999999999999</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>0.99</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1697</v>
+        <v>-0.0954</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.2425</v>
+        <v>-2.385</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>0.83</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.649</v>
+        <v>-0.5888</v>
       </c>
       <c r="J11" t="n">
-        <v>-16.225</v>
+        <v>-14.72</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.21</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4198</v>
+        <v>0.4796</v>
       </c>
       <c r="J12" t="n">
-        <v>11.3346</v>
+        <v>12.9492</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>1.07</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1991</v>
+        <v>0.1997</v>
       </c>
       <c r="J13" t="n">
-        <v>5.3757</v>
+        <v>5.3919</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>1.07</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1991</v>
+        <v>0.1997</v>
       </c>
       <c r="J14" t="n">
-        <v>5.3757</v>
+        <v>5.3919</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.77</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4114</v>
+        <v>-0.2613</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.1078</v>
+        <v>-7.0551</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.57</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.673</v>
+        <v>-0.45</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.171</v>
+        <v>-12.15</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.55</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3358</v>
+        <v>1.2132</v>
       </c>
       <c r="J17" t="n">
-        <v>36.0666</v>
+        <v>32.7564</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.33</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8778</v>
+        <v>0.8718</v>
       </c>
       <c r="J18" t="n">
-        <v>23.7006</v>
+        <v>23.5386</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2222</v>
+        <v>0.2811</v>
       </c>
       <c r="J19" t="n">
-        <v>5.9994</v>
+        <v>7.5897</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3499</v>
+        <v>-0.275</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.4473</v>
+        <v>-7.425</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3499</v>
+        <v>-0.275</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.4473</v>
+        <v>-7.425</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0641</v>
+        <v>1.0291</v>
       </c>
       <c r="J22" t="n">
-        <v>36.1794</v>
+        <v>34.9894</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.23</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.6692</v>
       </c>
       <c r="J23" t="n">
-        <v>23.8374</v>
+        <v>22.7528</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1659</v>
+        <v>-0.1103</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.6406</v>
+        <v>-3.7502</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>0.92</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3706</v>
+        <v>-0.3093</v>
       </c>
       <c r="J25" t="n">
-        <v>-12.6004</v>
+        <v>-10.5162</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.82</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6429</v>
+        <v>-0.5886</v>
       </c>
       <c r="J26" t="n">
-        <v>-21.8586</v>
+        <v>-20.0124</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.08</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2031</v>
+        <v>0.2114</v>
       </c>
       <c r="J27" t="n">
-        <v>6.9054</v>
+        <v>7.1876</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1466</v>
+        <v>0.145</v>
       </c>
       <c r="J28" t="n">
-        <v>4.9844</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>0.93</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1641</v>
+        <v>-0.0974</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.5794</v>
+        <v>-3.3116</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2013</v>
+        <v>-0.1202</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.8442</v>
+        <v>-4.0868</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.9</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2191</v>
+        <v>-0.1314</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.4494</v>
+        <v>-4.4676</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8427</v>
+        <v>0.8232</v>
       </c>
       <c r="J32" t="n">
-        <v>21.9102</v>
+        <v>21.4032</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5205</v>
+        <v>0.5044</v>
       </c>
       <c r="J33" t="n">
-        <v>13.533</v>
+        <v>13.1144</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.14</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4351</v>
+        <v>0.4271</v>
       </c>
       <c r="J34" t="n">
-        <v>11.3126</v>
+        <v>11.1046</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>0.99</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1444</v>
+        <v>-0.0803</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.7544</v>
+        <v>-2.0878</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2948</v>
+        <v>-0.2269</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.6648</v>
+        <v>-5.8994</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3892</v>
+        <v>0.444</v>
       </c>
       <c r="J37" t="n">
-        <v>10.1192</v>
+        <v>11.544</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2341</v>
+        <v>0.2505</v>
       </c>
       <c r="J38" t="n">
-        <v>6.0866</v>
+        <v>6.513</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.162</v>
+        <v>0.1653</v>
       </c>
       <c r="J39" t="n">
-        <v>4.212</v>
+        <v>4.2978</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3504</v>
+        <v>-0.217</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.1104</v>
+        <v>-5.642</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4639</v>
+        <v>-0.2961</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.0614</v>
+        <v>-7.6986</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>0.76</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.2827</v>
+        <v>-0.233</v>
       </c>
       <c r="J42" t="n">
-        <v>-6.5021</v>
+        <v>-5.359</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>0.73</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.3303</v>
+        <v>-0.2633</v>
       </c>
       <c r="J43" t="n">
-        <v>-7.5969</v>
+        <v>-6.0559</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>0.68</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.4136</v>
+        <v>-0.3111</v>
       </c>
       <c r="J44" t="n">
-        <v>-9.5128</v>
+        <v>-7.1553</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>0.62</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5286</v>
+        <v>-0.3645</v>
       </c>
       <c r="J45" t="n">
-        <v>-12.1578</v>
+        <v>-8.3835</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>0.52</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.674</v>
+        <v>-0.4576</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.502</v>
+        <v>-10.5248</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>1.4598</v>
+        <v>1.3048</v>
       </c>
       <c r="J47" t="n">
-        <v>33.5754</v>
+        <v>30.0104</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>1.49</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1277</v>
+        <v>1.0988</v>
       </c>
       <c r="J48" t="n">
-        <v>25.9371</v>
+        <v>25.2724</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>1.33</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7477</v>
+        <v>0.831</v>
       </c>
       <c r="J49" t="n">
-        <v>17.1971</v>
+        <v>19.113</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>1.2</v>
       </c>
       <c r="I50" t="n">
-        <v>0.434</v>
+        <v>0.5304</v>
       </c>
       <c r="J50" t="n">
-        <v>9.981999999999999</v>
+        <v>12.1992</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>1.08</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1214</v>
+        <v>0.2092</v>
       </c>
       <c r="J51" t="n">
-        <v>2.7922</v>
+        <v>4.8116</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.16</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3301</v>
+        <v>0.3689</v>
       </c>
       <c r="J52" t="n">
-        <v>9.572900000000001</v>
+        <v>10.6981</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2993</v>
+        <v>0.3303</v>
       </c>
       <c r="J53" t="n">
-        <v>8.6797</v>
+        <v>9.5787</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>0.99</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0245</v>
+        <v>-0.0197</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.7105</v>
+        <v>-0.5713</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.91</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.205</v>
+        <v>-0.1213</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.945</v>
+        <v>-3.5177</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.72</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4909</v>
+        <v>-0.3154</v>
       </c>
       <c r="J56" t="n">
-        <v>-14.2361</v>
+        <v>-9.146599999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.4</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0594</v>
+        <v>1.0292</v>
       </c>
       <c r="J57" t="n">
-        <v>30.7226</v>
+        <v>29.8468</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.15</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4597</v>
+        <v>0.4517</v>
       </c>
       <c r="J58" t="n">
-        <v>13.3313</v>
+        <v>13.0993</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>1.12</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3651</v>
+        <v>0.3738</v>
       </c>
       <c r="J59" t="n">
-        <v>10.5879</v>
+        <v>10.8402</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>1.07</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1921</v>
+        <v>0.2348</v>
       </c>
       <c r="J60" t="n">
-        <v>5.5709</v>
+        <v>6.8092</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6085</v>
+        <v>-0.5486</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.6465</v>
+        <v>-15.9094</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.68</v>
       </c>
       <c r="I62" t="n">
-        <v>1.5228</v>
+        <v>1.342</v>
       </c>
       <c r="J62" t="n">
-        <v>36.5472</v>
+        <v>32.208</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.48</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1357</v>
+        <v>1.0961</v>
       </c>
       <c r="J63" t="n">
-        <v>27.2568</v>
+        <v>26.3064</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>1.26</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6105</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>14.652</v>
+        <v>16.44</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>1.06</v>
       </c>
       <c r="I65" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.1616</v>
       </c>
       <c r="J65" t="n">
-        <v>1.9248</v>
+        <v>3.8784</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.99</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2119</v>
+        <v>-0.1264</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.0856</v>
+        <v>-3.0336</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.16</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4021</v>
+        <v>0.4516</v>
       </c>
       <c r="J67" t="n">
-        <v>9.650399999999999</v>
+        <v>10.8384</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.12</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3401</v>
+        <v>0.3677</v>
       </c>
       <c r="J68" t="n">
-        <v>8.1624</v>
+        <v>8.8248</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1544</v>
+        <v>-0.1331</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.7056</v>
+        <v>-3.1944</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.45</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7944</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>-19.0656</v>
+        <v>-13.0272</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.37</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8883</v>
+        <v>-0.6157</v>
       </c>
       <c r="J71" t="n">
-        <v>-21.3192</v>
+        <v>-14.7768</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>0.92</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.098</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J72" t="n">
-        <v>-2.254</v>
+        <v>-2.1344</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>0.91</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1163</v>
+        <v>-0.1045</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.6749</v>
+        <v>-2.4035</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>0.87</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1881</v>
+        <v>-0.1488</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.3263</v>
+        <v>-3.4224</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>0.72</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4504</v>
+        <v>-0.2954</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.3592</v>
+        <v>-6.7942</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4504</v>
+        <v>-0.2954</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.3592</v>
+        <v>-6.7942</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.79</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0007</v>
+        <v>0.9176</v>
       </c>
       <c r="J77" t="n">
-        <v>23.0161</v>
+        <v>21.1048</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.54</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7341</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>16.8843</v>
+        <v>15.1064</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>1.16</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2168</v>
+        <v>0.2273</v>
       </c>
       <c r="J79" t="n">
-        <v>4.9864</v>
+        <v>5.2279</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.89</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2973</v>
+        <v>-0.171</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.8379</v>
+        <v>-3.933</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.87</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3275</v>
+        <v>-0.1926</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.5325</v>
+        <v>-4.4298</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.93</v>
       </c>
       <c r="I82" t="n">
-        <v>1.8721</v>
+        <v>1.5848</v>
       </c>
       <c r="J82" t="n">
-        <v>37.442</v>
+        <v>31.696</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.93</v>
       </c>
       <c r="I83" t="n">
-        <v>1.8721</v>
+        <v>1.5848</v>
       </c>
       <c r="J83" t="n">
-        <v>37.442</v>
+        <v>31.696</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1.64</v>
       </c>
       <c r="I84" t="n">
-        <v>1.3556</v>
+        <v>1.2557</v>
       </c>
       <c r="J84" t="n">
-        <v>27.112</v>
+        <v>25.114</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>1.03</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.0174</v>
       </c>
       <c r="J85" t="n">
-        <v>-1.4</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.98</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3008</v>
+        <v>-0.211</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.016</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>0.77</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.2284</v>
+        <v>-0.202</v>
       </c>
       <c r="J87" t="n">
-        <v>-4.568</v>
+        <v>-4.04</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>0.7</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.3365</v>
+        <v>-0.2765</v>
       </c>
       <c r="J88" t="n">
-        <v>-6.73</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>0.61</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4822</v>
+        <v>-0.3641</v>
       </c>
       <c r="J89" t="n">
-        <v>-9.644</v>
+        <v>-7.282</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.54</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.615</v>
+        <v>-0.4261</v>
       </c>
       <c r="J90" t="n">
-        <v>-12.3</v>
+        <v>-8.522</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.34</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8894</v>
+        <v>-0.6162</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.788</v>
+        <v>-12.324</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.41</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0585</v>
+        <v>1.0323</v>
       </c>
       <c r="J92" t="n">
-        <v>26.4625</v>
+        <v>25.8075</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.33</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8844</v>
+        <v>0.8759</v>
       </c>
       <c r="J93" t="n">
-        <v>22.11</v>
+        <v>21.8975</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1983</v>
+        <v>0.2548</v>
       </c>
       <c r="J94" t="n">
-        <v>4.9575</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>1.04</v>
       </c>
       <c r="I95" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.1297</v>
       </c>
       <c r="J95" t="n">
-        <v>1.7125</v>
+        <v>3.2425</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.93</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3763</v>
+        <v>-0.3032</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.407500000000001</v>
+        <v>-7.58</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.32</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.6651</v>
       </c>
       <c r="J97" t="n">
-        <v>13.925</v>
+        <v>16.6275</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>1.14</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3051</v>
+        <v>0.3352</v>
       </c>
       <c r="J98" t="n">
-        <v>7.6275</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>1.13</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2893</v>
+        <v>0.3155</v>
       </c>
       <c r="J99" t="n">
-        <v>7.2325</v>
+        <v>7.8875</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>0.65</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5788</v>
+        <v>-0.3796</v>
       </c>
       <c r="J100" t="n">
-        <v>-14.47</v>
+        <v>-9.49</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.6</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6411</v>
+        <v>-0.4258</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.0275</v>
+        <v>-10.645</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.57</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3706</v>
+        <v>1.2365</v>
       </c>
       <c r="J102" t="n">
-        <v>34.265</v>
+        <v>30.9125</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.15</v>
       </c>
       <c r="I103" t="n">
-        <v>0.393</v>
+        <v>0.4414</v>
       </c>
       <c r="J103" t="n">
-        <v>9.824999999999999</v>
+        <v>11.035</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>1.13</v>
       </c>
       <c r="I104" t="n">
-        <v>0.335</v>
+        <v>0.3894</v>
       </c>
       <c r="J104" t="n">
-        <v>8.375</v>
+        <v>9.734999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>1.1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2476</v>
+        <v>0.3076</v>
       </c>
       <c r="J105" t="n">
-        <v>6.19</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3526</v>
+        <v>-0.2771</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.815</v>
+        <v>-6.9275</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.14</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3527</v>
+        <v>0.3855</v>
       </c>
       <c r="J107" t="n">
-        <v>8.817500000000001</v>
+        <v>9.637499999999999</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>0.84</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2589</v>
+        <v>-0.1807</v>
       </c>
       <c r="J108" t="n">
-        <v>-6.4725</v>
+        <v>-4.5175</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>0.82</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2982</v>
+        <v>-0.2001</v>
       </c>
       <c r="J109" t="n">
-        <v>-7.455</v>
+        <v>-5.0025</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3157</v>
+        <v>-0.2099</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.8925</v>
+        <v>-5.2475</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.6</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6177</v>
+        <v>-0.4106</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.4425</v>
+        <v>-10.265</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.55</v>
       </c>
       <c r="I112" t="n">
-        <v>1.3318</v>
+        <v>1.2111</v>
       </c>
       <c r="J112" t="n">
-        <v>39.954</v>
+        <v>36.333</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.37</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9565</v>
       </c>
       <c r="J113" t="n">
-        <v>28.866</v>
+        <v>28.695</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.36</v>
       </c>
       <c r="I114" t="n">
-        <v>0.9403</v>
+        <v>0.9359</v>
       </c>
       <c r="J114" t="n">
-        <v>28.209</v>
+        <v>28.077</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>0.85</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6018</v>
+        <v>-0.5377</v>
       </c>
       <c r="J115" t="n">
-        <v>-18.054</v>
+        <v>-16.131</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.76</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.8175</v>
+        <v>-0.7716</v>
       </c>
       <c r="J116" t="n">
-        <v>-24.525</v>
+        <v>-23.148</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.15</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3427</v>
+        <v>0.3763</v>
       </c>
       <c r="J117" t="n">
-        <v>10.281</v>
+        <v>11.289</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.09</v>
       </c>
       <c r="I118" t="n">
-        <v>0.246</v>
+        <v>0.253</v>
       </c>
       <c r="J118" t="n">
-        <v>7.38</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.91</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1619</v>
+        <v>-0.1143</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.857</v>
+        <v>-3.429</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.9</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1874</v>
+        <v>-0.1248</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.622</v>
+        <v>-3.744</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.49</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.764</v>
+        <v>-0.5193</v>
       </c>
       <c r="J121" t="n">
-        <v>-22.92</v>
+        <v>-15.579</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9036</v>
+        <v>0.8822</v>
       </c>
       <c r="J122" t="n">
-        <v>26.2044</v>
+        <v>25.5838</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.24</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7173</v>
+        <v>0.6887</v>
       </c>
       <c r="J123" t="n">
-        <v>20.8017</v>
+        <v>19.9723</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>1.05</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1482</v>
+        <v>0.1806</v>
       </c>
       <c r="J124" t="n">
-        <v>4.2978</v>
+        <v>5.2374</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>0.9</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4352</v>
+        <v>-0.3722</v>
       </c>
       <c r="J125" t="n">
-        <v>-12.6208</v>
+        <v>-10.7938</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.9</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4352</v>
+        <v>-0.3722</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.6208</v>
+        <v>-10.7938</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.24</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4696</v>
+        <v>0.5447</v>
       </c>
       <c r="J127" t="n">
-        <v>13.6184</v>
+        <v>15.7963</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>0.91</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.172</v>
+        <v>-0.1147</v>
       </c>
       <c r="J128" t="n">
-        <v>-4.988</v>
+        <v>-3.3263</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>0.89</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2121</v>
+        <v>-0.1362</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.1509</v>
+        <v>-3.9498</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.86</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2654</v>
+        <v>-0.1678</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.6966</v>
+        <v>-4.8662</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5298</v>
+        <v>-0.3452</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.3642</v>
+        <v>-10.0108</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.56</v>
       </c>
       <c r="I132" t="n">
-        <v>1.4095</v>
+        <v>1.2603</v>
       </c>
       <c r="J132" t="n">
-        <v>42.285</v>
+        <v>37.809</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>1.04</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1241</v>
+        <v>0.1516</v>
       </c>
       <c r="J133" t="n">
-        <v>3.723</v>
+        <v>4.548</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>1.01</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0003</v>
+        <v>0.0403</v>
       </c>
       <c r="J134" t="n">
-        <v>0.008999999999999999</v>
+        <v>1.209</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.98</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1647</v>
+        <v>-0.1098</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.941</v>
+        <v>-3.294</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.74</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.834</v>
+        <v>-0.7932</v>
       </c>
       <c r="J136" t="n">
-        <v>-25.02</v>
+        <v>-23.796</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.37</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5946</v>
+        <v>0.7197</v>
       </c>
       <c r="J137" t="n">
-        <v>17.838</v>
+        <v>21.591</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.134</v>
+        <v>0.1539</v>
       </c>
       <c r="J138" t="n">
-        <v>4.02</v>
+        <v>4.617</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0264</v>
+        <v>-0.0034</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.792</v>
+        <v>-0.102</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.96</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1311</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.933</v>
+        <v>-2.028</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.83</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3499</v>
+        <v>-0.2137</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.497</v>
+        <v>-6.411</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.52</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8486</v>
+        <v>0.8359</v>
       </c>
       <c r="J142" t="n">
-        <v>18.6692</v>
+        <v>18.3898</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.73</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.4386</v>
+        <v>-0.2869</v>
       </c>
       <c r="J143" t="n">
-        <v>-9.6492</v>
+        <v>-6.3118</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.71</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.4675</v>
+        <v>-0.3061</v>
       </c>
       <c r="J144" t="n">
-        <v>-10.285</v>
+        <v>-6.7342</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.66</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5371</v>
+        <v>-0.3535</v>
       </c>
       <c r="J145" t="n">
-        <v>-11.8162</v>
+        <v>-7.777</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6672</v>
+        <v>-0.4469</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.6784</v>
+        <v>-9.831799999999999</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.6</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7981</v>
+        <v>0.7185</v>
       </c>
       <c r="J147" t="n">
-        <v>17.5582</v>
+        <v>15.807</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5018</v>
+        <v>0.4479</v>
       </c>
       <c r="J148" t="n">
-        <v>11.0396</v>
+        <v>9.8538</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.24</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3347</v>
+        <v>0.3243</v>
       </c>
       <c r="J149" t="n">
-        <v>7.3634</v>
+        <v>7.1346</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.22</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3041</v>
+        <v>0.3007</v>
       </c>
       <c r="J150" t="n">
-        <v>6.6902</v>
+        <v>6.6154</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.89</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2988</v>
+        <v>-0.1719</v>
       </c>
       <c r="J151" t="n">
-        <v>-6.5736</v>
+        <v>-3.7818</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.35</v>
       </c>
       <c r="I152" t="n">
-        <v>1.0003</v>
+        <v>0.9735</v>
       </c>
       <c r="J152" t="n">
-        <v>29.0087</v>
+        <v>28.2315</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.16</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5044</v>
       </c>
       <c r="J153" t="n">
-        <v>15.8601</v>
+        <v>14.6276</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.52</v>
+        <v>0.4777</v>
       </c>
       <c r="J154" t="n">
-        <v>15.08</v>
+        <v>13.8533</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.87</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4961</v>
+        <v>-0.4419</v>
       </c>
       <c r="J155" t="n">
-        <v>-14.3869</v>
+        <v>-12.8151</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.1095</v>
+        <v>-1.0991</v>
       </c>
       <c r="J156" t="n">
-        <v>-32.1755</v>
+        <v>-31.8739</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.51</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7786</v>
+        <v>0.969</v>
       </c>
       <c r="J157" t="n">
-        <v>22.5794</v>
+        <v>28.101</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.23</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4295</v>
+        <v>0.4968</v>
       </c>
       <c r="J158" t="n">
-        <v>12.4555</v>
+        <v>14.4072</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>1.16</v>
       </c>
       <c r="I159" t="n">
-        <v>0.328</v>
+        <v>0.367</v>
       </c>
       <c r="J159" t="n">
-        <v>9.512</v>
+        <v>10.643</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>0.63</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.6075</v>
+        <v>-0.4006</v>
       </c>
       <c r="J160" t="n">
-        <v>-17.6175</v>
+        <v>-11.6174</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.42</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.853</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="J161" t="n">
-        <v>-24.737</v>
+        <v>-17.0868</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.45</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6181</v>
+        <v>0.5533</v>
       </c>
       <c r="J162" t="n">
-        <v>14.2163</v>
+        <v>12.7259</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.31</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4353</v>
+        <v>0.4003</v>
       </c>
       <c r="J163" t="n">
-        <v>10.0119</v>
+        <v>9.206899999999999</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.27</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3675</v>
+        <v>0.3562</v>
       </c>
       <c r="J164" t="n">
-        <v>8.452500000000001</v>
+        <v>8.192600000000001</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.22</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2939</v>
+        <v>0.2978</v>
       </c>
       <c r="J165" t="n">
-        <v>6.7597</v>
+        <v>6.8494</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>1.2</v>
       </c>
       <c r="I166" t="n">
-        <v>0.2649</v>
+        <v>0.2734</v>
       </c>
       <c r="J166" t="n">
-        <v>6.0927</v>
+        <v>6.2882</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>0.85</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.1673</v>
+        <v>-0.1504</v>
       </c>
       <c r="J167" t="n">
-        <v>-3.8479</v>
+        <v>-3.4592</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>0.79</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2651</v>
+        <v>-0.2141</v>
       </c>
       <c r="J168" t="n">
-        <v>-6.0973</v>
+        <v>-4.9243</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.75</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3313</v>
+        <v>-0.2537</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.6199</v>
+        <v>-5.8351</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4474</v>
+        <v>-0.3084</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.2902</v>
+        <v>-7.0932</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.51</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7038</v>
+        <v>-0.4763</v>
       </c>
       <c r="J171" t="n">
-        <v>-16.1874</v>
+        <v>-10.9549</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.3</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5109</v>
+        <v>0.6069</v>
       </c>
       <c r="J172" t="n">
-        <v>13.7943</v>
+        <v>16.3863</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.24</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4304</v>
+        <v>0.502</v>
       </c>
       <c r="J173" t="n">
-        <v>11.6208</v>
+        <v>13.554</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>1.13</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2671</v>
+        <v>0.2991</v>
       </c>
       <c r="J174" t="n">
-        <v>7.2117</v>
+        <v>8.075699999999999</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2692</v>
+        <v>-0.1593</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.2684</v>
+        <v>-4.3011</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.59</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6617</v>
+        <v>-0.4411</v>
       </c>
       <c r="J176" t="n">
-        <v>-17.8659</v>
+        <v>-11.9097</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.43</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1569</v>
+        <v>1.0913</v>
       </c>
       <c r="J177" t="n">
-        <v>31.2363</v>
+        <v>29.4651</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1361</v>
+        <v>1.0777</v>
       </c>
       <c r="J178" t="n">
-        <v>30.6747</v>
+        <v>29.0979</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.86</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.5334</v>
+        <v>-0.4764</v>
       </c>
       <c r="J179" t="n">
-        <v>-14.4018</v>
+        <v>-12.8628</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.6622</v>
+        <v>-0.6103</v>
       </c>
       <c r="J180" t="n">
-        <v>-17.8794</v>
+        <v>-16.4781</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.74</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8298</v>
+        <v>-0.7893</v>
       </c>
       <c r="J181" t="n">
-        <v>-22.4046</v>
+        <v>-21.3111</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.18</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4105</v>
+        <v>0.463</v>
       </c>
       <c r="J182" t="n">
-        <v>10.673</v>
+        <v>12.038</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>0.95</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0495</v>
+        <v>-0.0592</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.287</v>
+        <v>-1.5392</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>0.91</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1259</v>
+        <v>-0.1076</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.2734</v>
+        <v>-2.7976</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>0.64</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.5669</v>
+        <v>-0.374</v>
       </c>
       <c r="J185" t="n">
-        <v>-14.7394</v>
+        <v>-9.724</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6696</v>
+        <v>-0.4484</v>
       </c>
       <c r="J186" t="n">
-        <v>-17.4096</v>
+        <v>-11.6584</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.51</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1899</v>
+        <v>1.131</v>
       </c>
       <c r="J187" t="n">
-        <v>30.9374</v>
+        <v>29.406</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.5</v>
       </c>
       <c r="I188" t="n">
-        <v>1.1697</v>
+        <v>1.1186</v>
       </c>
       <c r="J188" t="n">
-        <v>30.4122</v>
+        <v>29.0836</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>1.23</v>
       </c>
       <c r="I189" t="n">
-        <v>0.527</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J189" t="n">
-        <v>13.702</v>
+        <v>15.9224</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4525</v>
+        <v>0.5399</v>
       </c>
       <c r="J190" t="n">
-        <v>11.765</v>
+        <v>14.0374</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>1.1</v>
       </c>
       <c r="I191" t="n">
-        <v>0.1919</v>
+        <v>0.2772</v>
       </c>
       <c r="J191" t="n">
-        <v>4.9894</v>
+        <v>7.2072</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.16</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3979</v>
+        <v>0.4457</v>
       </c>
       <c r="J192" t="n">
-        <v>9.9475</v>
+        <v>11.1425</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>0.9</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.124</v>
+        <v>-0.1123</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.1</v>
+        <v>-2.8075</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>0.87</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1767</v>
+        <v>-0.1457</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.4175</v>
+        <v>-3.6425</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.6</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.6092</v>
+        <v>-0.4056</v>
       </c>
       <c r="J195" t="n">
-        <v>-15.23</v>
+        <v>-10.14</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>0.5</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7357</v>
+        <v>-0.4982</v>
       </c>
       <c r="J196" t="n">
-        <v>-18.3925</v>
+        <v>-12.455</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.69</v>
       </c>
       <c r="I197" t="n">
-        <v>1.5568</v>
+        <v>1.3628</v>
       </c>
       <c r="J197" t="n">
-        <v>38.92</v>
+        <v>34.07</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.47</v>
       </c>
       <c r="I198" t="n">
-        <v>1.1319</v>
+        <v>1.09</v>
       </c>
       <c r="J198" t="n">
-        <v>28.2975</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>1.2</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4768</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="J199" t="n">
-        <v>11.92</v>
+        <v>13.7475</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>1.03</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.007</v>
+        <v>0.0698</v>
       </c>
       <c r="J200" t="n">
-        <v>-0.175</v>
+        <v>1.745</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4653</v>
+        <v>-0.3888</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.6325</v>
+        <v>-9.720000000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1.56</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9064</v>
+        <v>1.1099</v>
       </c>
       <c r="J202" t="n">
-        <v>21.7536</v>
+        <v>26.6376</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.78</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.3484</v>
+        <v>-0.2352</v>
       </c>
       <c r="J203" t="n">
-        <v>-8.361599999999999</v>
+        <v>-5.6448</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.59</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.6227</v>
+        <v>-0.4152</v>
       </c>
       <c r="J204" t="n">
-        <v>-14.9448</v>
+        <v>-9.9648</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.57</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.6485</v>
+        <v>-0.4338</v>
       </c>
       <c r="J205" t="n">
-        <v>-15.564</v>
+        <v>-10.4112</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.54</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6865</v>
+        <v>-0.4616</v>
       </c>
       <c r="J206" t="n">
-        <v>-16.476</v>
+        <v>-11.0784</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.85</v>
       </c>
       <c r="I207" t="n">
-        <v>1.8362</v>
+        <v>1.5521</v>
       </c>
       <c r="J207" t="n">
-        <v>44.0688</v>
+        <v>37.2504</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.29</v>
       </c>
       <c r="I208" t="n">
-        <v>0.7214</v>
+        <v>0.755</v>
       </c>
       <c r="J208" t="n">
-        <v>17.3136</v>
+        <v>18.12</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>1.2</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4712</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="J209" t="n">
-        <v>11.3088</v>
+        <v>13.1496</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>1.11</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2337</v>
+        <v>0.3141</v>
       </c>
       <c r="J210" t="n">
-        <v>5.6088</v>
+        <v>7.5384</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.9</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4954</v>
+        <v>-0.4203</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.8896</v>
+        <v>-10.0872</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.38</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0824</v>
+        <v>1.0394</v>
       </c>
       <c r="J212" t="n">
-        <v>29.2248</v>
+        <v>28.0638</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>1.13</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4842</v>
+        <v>0.4344</v>
       </c>
       <c r="J213" t="n">
-        <v>13.0734</v>
+        <v>11.7288</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.302</v>
+        <v>-0.2594</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.154</v>
+        <v>-7.0038</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.78</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.6722</v>
       </c>
       <c r="J215" t="n">
-        <v>-19.3374</v>
+        <v>-18.1494</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.77</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7406</v>
+        <v>-0.6978</v>
       </c>
       <c r="J216" t="n">
-        <v>-19.9962</v>
+        <v>-18.8406</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.75</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0196</v>
+        <v>1.1904</v>
       </c>
       <c r="J217" t="n">
-        <v>27.5292</v>
+        <v>32.1408</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>0.98</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0886</v>
+        <v>-0.0404</v>
       </c>
       <c r="J218" t="n">
-        <v>-2.3922</v>
+        <v>-1.0908</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>0.95</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1524</v>
+        <v>-0.0808</v>
       </c>
       <c r="J219" t="n">
-        <v>-4.1148</v>
+        <v>-2.1816</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>0.86</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3056</v>
+        <v>-0.1829</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.251200000000001</v>
+        <v>-4.9383</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5285</v>
+        <v>-0.3415</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.2695</v>
+        <v>-9.220499999999999</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.8</v>
       </c>
       <c r="I222" t="n">
-        <v>1.6386</v>
+        <v>1.4335</v>
       </c>
       <c r="J222" t="n">
-        <v>31.1334</v>
+        <v>27.2365</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>1.78</v>
       </c>
       <c r="I223" t="n">
-        <v>1.6029</v>
+        <v>1.411</v>
       </c>
       <c r="J223" t="n">
-        <v>30.4551</v>
+        <v>26.809</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>1.67</v>
       </c>
       <c r="I224" t="n">
-        <v>1.3997</v>
+        <v>1.2861</v>
       </c>
       <c r="J224" t="n">
-        <v>26.5943</v>
+        <v>24.4359</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>1.44</v>
       </c>
       <c r="I225" t="n">
-        <v>0.9001</v>
+        <v>1.0155</v>
       </c>
       <c r="J225" t="n">
-        <v>17.1019</v>
+        <v>19.2945</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.97</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3421</v>
+        <v>-0.2536</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.4999</v>
+        <v>-4.8184</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>0.97</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1265</v>
+        <v>0.1146</v>
       </c>
       <c r="J227" t="n">
-        <v>2.4035</v>
+        <v>2.1774</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>0.52</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.6348</v>
+        <v>-0.4408</v>
       </c>
       <c r="J228" t="n">
-        <v>-12.0612</v>
+        <v>-8.3752</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>0.49</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.6804</v>
+        <v>-0.4688</v>
       </c>
       <c r="J229" t="n">
-        <v>-12.9276</v>
+        <v>-8.9072</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.44</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.7518</v>
+        <v>-0.5163</v>
       </c>
       <c r="J230" t="n">
-        <v>-14.2842</v>
+        <v>-9.809699999999999</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.44</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.7518</v>
+        <v>-0.5163</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.2842</v>
+        <v>-9.809699999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>1.47</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2547</v>
+        <v>1.1557</v>
       </c>
       <c r="J232" t="n">
-        <v>35.1316</v>
+        <v>32.3596</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>1.08</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3179</v>
+        <v>0.2828</v>
       </c>
       <c r="J233" t="n">
-        <v>8.901199999999999</v>
+        <v>7.9184</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>1.06</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2513</v>
+        <v>0.2224</v>
       </c>
       <c r="J234" t="n">
-        <v>7.0364</v>
+        <v>6.2272</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>0.77</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.7501</v>
+        <v>-0.7056</v>
       </c>
       <c r="J235" t="n">
-        <v>-21.0028</v>
+        <v>-19.7568</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.74</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.821</v>
+        <v>-0.7814</v>
       </c>
       <c r="J236" t="n">
-        <v>-22.988</v>
+        <v>-21.8792</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.24</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4318</v>
+        <v>0.5033</v>
       </c>
       <c r="J237" t="n">
-        <v>12.0904</v>
+        <v>14.0924</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.17</v>
       </c>
       <c r="I238" t="n">
-        <v>0.331</v>
+        <v>0.376</v>
       </c>
       <c r="J238" t="n">
-        <v>9.268000000000001</v>
+        <v>10.528</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>1.06</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1444</v>
+        <v>0.1571</v>
       </c>
       <c r="J239" t="n">
-        <v>4.0432</v>
+        <v>4.3988</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>0.87</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2841</v>
+        <v>-0.1696</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.9548</v>
+        <v>-4.7488</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.78</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4172</v>
+        <v>-0.2617</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.6816</v>
+        <v>-7.3276</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>2.06</v>
       </c>
       <c r="I242" t="n">
-        <v>2.0529</v>
+        <v>1.772</v>
       </c>
       <c r="J242" t="n">
-        <v>45.1638</v>
+        <v>38.984</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.44</v>
       </c>
       <c r="I243" t="n">
-        <v>1.0252</v>
+        <v>1.0363</v>
       </c>
       <c r="J243" t="n">
-        <v>22.5544</v>
+        <v>22.7986</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>1.18</v>
       </c>
       <c r="I244" t="n">
-        <v>0.387</v>
+        <v>0.4818</v>
       </c>
       <c r="J244" t="n">
-        <v>8.513999999999999</v>
+        <v>10.5996</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>1.09</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1516</v>
+        <v>0.2399</v>
       </c>
       <c r="J245" t="n">
-        <v>3.3352</v>
+        <v>5.2778</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.96</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3373</v>
+        <v>-0.2514</v>
       </c>
       <c r="J246" t="n">
-        <v>-7.4206</v>
+        <v>-5.5308</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>0.86</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1439</v>
+        <v>-0.1358</v>
       </c>
       <c r="J247" t="n">
-        <v>-3.1658</v>
+        <v>-2.9876</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>0.82</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2092</v>
+        <v>-0.1798</v>
       </c>
       <c r="J248" t="n">
-        <v>-4.6024</v>
+        <v>-3.9556</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.75</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3226</v>
+        <v>-0.2515</v>
       </c>
       <c r="J249" t="n">
-        <v>-7.0972</v>
+        <v>-5.533</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.61</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5634</v>
+        <v>-0.3805</v>
       </c>
       <c r="J250" t="n">
-        <v>-12.3948</v>
+        <v>-8.371</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.48</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.7388</v>
+        <v>-0.5021</v>
       </c>
       <c r="J251" t="n">
-        <v>-16.2536</v>
+        <v>-11.0462</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.6</v>
       </c>
       <c r="I252" t="n">
-        <v>1.384</v>
+        <v>1.2502</v>
       </c>
       <c r="J252" t="n">
-        <v>31.832</v>
+        <v>28.7546</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.45</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0855</v>
+        <v>1.0626</v>
       </c>
       <c r="J253" t="n">
-        <v>24.9665</v>
+        <v>24.4398</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>1.2</v>
       </c>
       <c r="I254" t="n">
-        <v>0.4712</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="J254" t="n">
-        <v>10.8376</v>
+        <v>12.6017</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>1.18</v>
       </c>
       <c r="I255" t="n">
-        <v>0.4197</v>
+        <v>0.4984</v>
       </c>
       <c r="J255" t="n">
-        <v>9.6531</v>
+        <v>11.4632</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.92</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4397</v>
+        <v>-0.3614</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.1131</v>
+        <v>-8.312200000000001</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.21</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4889</v>
+        <v>0.574</v>
       </c>
       <c r="J257" t="n">
-        <v>11.2447</v>
+        <v>13.202</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>0.8</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2742</v>
+        <v>-0.2117</v>
       </c>
       <c r="J258" t="n">
-        <v>-6.3066</v>
+        <v>-4.8691</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>0.67</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.5</v>
+        <v>-0.3337</v>
       </c>
       <c r="J259" t="n">
-        <v>-11.5</v>
+        <v>-7.6751</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.67</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.5</v>
+        <v>-0.3337</v>
       </c>
       <c r="J260" t="n">
-        <v>-11.5</v>
+        <v>-7.6751</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.47</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7645</v>
+        <v>-0.5202</v>
       </c>
       <c r="J261" t="n">
-        <v>-17.5835</v>
+        <v>-11.9646</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.14</v>
       </c>
       <c r="I262" t="n">
-        <v>0.2978</v>
+        <v>0.3292</v>
       </c>
       <c r="J262" t="n">
-        <v>8.933999999999999</v>
+        <v>9.875999999999999</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.07</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1793</v>
+        <v>0.1864</v>
       </c>
       <c r="J263" t="n">
-        <v>5.379</v>
+        <v>5.592</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.02</v>
       </c>
       <c r="I264" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="J264" t="n">
-        <v>2.232</v>
+        <v>2.043</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.97</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.049</v>
       </c>
       <c r="J265" t="n">
-        <v>-2.58</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.74</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4648</v>
+        <v>-0.2966</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.944</v>
+        <v>-8.898</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.21</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6744</v>
+        <v>0.6339</v>
       </c>
       <c r="J267" t="n">
-        <v>20.232</v>
+        <v>19.017</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.6239</v>
+        <v>0.5824</v>
       </c>
       <c r="J268" t="n">
-        <v>18.717</v>
+        <v>17.472</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.98</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1423</v>
+        <v>-0.1005</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.269</v>
+        <v>-3.015</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.97</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1825</v>
+        <v>-0.1374</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.475</v>
+        <v>-4.122</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.8</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6791</v>
+        <v>-0.6301</v>
       </c>
       <c r="J271" t="n">
-        <v>-20.373</v>
+        <v>-18.903</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6477/event_6477_evp_summary.xlsx
+++ b/database/event/6477/event_6477_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.9612</v>
+        <v>4.5897</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5435</v>
+        <v>0.5028</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6017</v>
+        <v>1.4651</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9612</v>
+        <v>4.5897</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6616</v>
+        <v>4.3178</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2996</v>
+        <v>0.2719</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8761</v>
+        <v>6.7254</v>
       </c>
       <c r="I2" t="n">
-        <v>6.8761</v>
+        <v>6.7254</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2996</v>
+        <v>0.2719</v>
       </c>
       <c r="K2" t="n">
         <v>155</v>
@@ -529,7 +529,7 @@
         <v>52</v>
       </c>
       <c r="M2" t="n">
-        <v>7.1757</v>
+        <v>6.997299999999999</v>
       </c>
       <c r="N2" t="n">
         <v>207</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.7371</v>
+        <v>4.5701</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5189</v>
+        <v>0.5006</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5006</v>
+        <v>1.4562</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7371</v>
+        <v>4.5701</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1127</v>
+        <v>3.8784</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6244</v>
+        <v>0.6917</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6709</v>
+        <v>5.7637</v>
       </c>
       <c r="I3" t="n">
-        <v>6.3997</v>
+        <v>6.2209</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6244</v>
+        <v>0.6917</v>
       </c>
       <c r="K3" t="n">
         <v>262</v>
@@ -575,7 +575,7 @@
         <v>52</v>
       </c>
       <c r="M3" t="n">
-        <v>7.0241</v>
+        <v>6.9126</v>
       </c>
       <c r="N3" t="n">
         <v>314</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4135</v>
+        <v>4.288</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4835</v>
+        <v>0.4697</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3545</v>
+        <v>1.3278</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4135</v>
+        <v>4.288</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4703</v>
+        <v>2.4325</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9432</v>
+        <v>1.8555</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4703</v>
+        <v>2.5991</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7878</v>
+        <v>2.8052</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9432</v>
+        <v>1.8555</v>
       </c>
       <c r="K4" t="n">
         <v>262</v>
@@ -621,7 +621,7 @@
         <v>52</v>
       </c>
       <c r="M4" t="n">
-        <v>4.731</v>
+        <v>4.6607</v>
       </c>
       <c r="N4" t="n">
         <v>314</v>
@@ -630,185 +630,185 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>anarkez</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.5934</v>
+        <v>3.2779</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3936</v>
+        <v>0.3591</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9842</v>
+        <v>0.868</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5934</v>
+        <v>3.2779</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5934</v>
+        <v>1.9535</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.3244</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5306</v>
+        <v>1.9535</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5306</v>
+        <v>2.1084</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.3244</v>
       </c>
       <c r="K5" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5306</v>
+        <v>3.4328</v>
       </c>
       <c r="N5" t="n">
-        <v>194</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>anarkez</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2809</v>
+        <v>3.249</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3594</v>
+        <v>0.3559</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8431</v>
+        <v>0.8548</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2809</v>
+        <v>3.249</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9284</v>
+        <v>3.249</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3525</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9284</v>
+        <v>4.3861</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1763</v>
+        <v>4.3861</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3525</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>262</v>
+        <v>194</v>
       </c>
       <c r="L6" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5288</v>
+        <v>4.3861</v>
       </c>
       <c r="N6" t="n">
-        <v>314</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>PlesseN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7419</v>
+        <v>2.4455</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3004</v>
+        <v>0.2679</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5998</v>
+        <v>0.489</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7419</v>
+        <v>2.4455</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7419</v>
+        <v>2.4455</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7419</v>
+        <v>2.6276</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7419</v>
+        <v>2.6276</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7419</v>
+        <v>2.6276</v>
       </c>
       <c r="N7" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PlesseN</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7146</v>
+        <v>2.4453</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2974</v>
+        <v>0.2679</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5875</v>
+        <v>0.4889</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7146</v>
+        <v>2.4453</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7146</v>
+        <v>2.4453</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7146</v>
+        <v>2.627</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7146</v>
+        <v>2.627</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7146</v>
+        <v>2.627</v>
       </c>
       <c r="N8" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5997</v>
+        <v>2.3991</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2848</v>
+        <v>0.2628</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5356</v>
+        <v>0.4679</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5997</v>
+        <v>2.3991</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5997</v>
+        <v>2.3991</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5997</v>
+        <v>2.526</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5997</v>
+        <v>2.526</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5997</v>
+        <v>2.526</v>
       </c>
       <c r="N9" t="n">
         <v>159</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5993</v>
+        <v>2.3766</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2847</v>
+        <v>0.2603</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5354</v>
+        <v>0.4577</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5993</v>
+        <v>2.3766</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9697</v>
+        <v>2.7267</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3704</v>
+        <v>-0.3501</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1611</v>
+        <v>3.243</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5674</v>
+        <v>3.5002</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3704</v>
+        <v>-0.3501</v>
       </c>
       <c r="K10" t="n">
         <v>262</v>
@@ -897,7 +897,7 @@
         <v>52</v>
       </c>
       <c r="M10" t="n">
-        <v>3.197</v>
+        <v>3.1501</v>
       </c>
       <c r="N10" t="n">
         <v>314</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2567</v>
+        <v>2.1896</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2472</v>
+        <v>0.2399</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3808</v>
+        <v>0.3725</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2567</v>
+        <v>2.1896</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2567</v>
+        <v>2.1896</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2567</v>
+        <v>2.1896</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2567</v>
+        <v>2.1896</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2567</v>
+        <v>2.1896</v>
       </c>
       <c r="N11" t="n">
         <v>194</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.007</v>
+        <v>1.956</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2199</v>
+        <v>0.2143</v>
       </c>
       <c r="D12" t="n">
-        <v>0.268</v>
+        <v>0.2662</v>
       </c>
       <c r="E12" t="n">
-        <v>2.007</v>
+        <v>1.956</v>
       </c>
       <c r="F12" t="n">
-        <v>1.795</v>
+        <v>1.7439</v>
       </c>
       <c r="G12" t="n">
-        <v>0.212</v>
+        <v>0.2121</v>
       </c>
       <c r="H12" t="n">
-        <v>1.795</v>
+        <v>1.7439</v>
       </c>
       <c r="I12" t="n">
-        <v>1.795</v>
+        <v>1.7439</v>
       </c>
       <c r="J12" t="n">
-        <v>0.212</v>
+        <v>0.2121</v>
       </c>
       <c r="K12" t="n">
         <v>155</v>
@@ -989,7 +989,7 @@
         <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>2.007</v>
+        <v>1.956</v>
       </c>
       <c r="N12" t="n">
         <v>207</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.879</v>
+        <v>1.7575</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2058</v>
+        <v>0.1925</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2103</v>
+        <v>0.1758</v>
       </c>
       <c r="E13" t="n">
-        <v>1.879</v>
+        <v>1.7575</v>
       </c>
       <c r="F13" t="n">
-        <v>1.879</v>
+        <v>1.7575</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.879</v>
+        <v>1.7575</v>
       </c>
       <c r="I13" t="n">
-        <v>1.879</v>
+        <v>1.7575</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.879</v>
+        <v>1.7575</v>
       </c>
       <c r="N13" t="n">
         <v>69</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4608</v>
+        <v>1.4377</v>
       </c>
       <c r="C14" t="n">
-        <v>0.16</v>
+        <v>0.1575</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0215</v>
+        <v>0.0303</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4608</v>
+        <v>1.4377</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4608</v>
+        <v>1.2857</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4608</v>
+        <v>1.2857</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4608</v>
+        <v>1.3877</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="K14" t="n">
-        <v>165</v>
+        <v>262</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4608</v>
+        <v>1.5397</v>
       </c>
       <c r="N14" t="n">
-        <v>165</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4149</v>
+        <v>1.4177</v>
       </c>
       <c r="C15" t="n">
-        <v>0.155</v>
+        <v>0.1553</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0007</v>
+        <v>0.0212</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4149</v>
+        <v>1.4177</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2723</v>
+        <v>1.4177</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1426</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2723</v>
+        <v>1.4177</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4358</v>
+        <v>1.4177</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1426</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>262</v>
+        <v>165</v>
       </c>
       <c r="L15" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5784</v>
+        <v>1.4177</v>
       </c>
       <c r="N15" t="n">
-        <v>314</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2344</v>
+        <v>1.2319</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1352</v>
+        <v>0.1349</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0634</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2344</v>
+        <v>1.2319</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2344</v>
+        <v>1.2319</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2344</v>
+        <v>1.2319</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2344</v>
+        <v>1.2319</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2344</v>
+        <v>1.2319</v>
       </c>
       <c r="N16" t="n">
         <v>159</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1687</v>
+        <v>1.1539</v>
       </c>
       <c r="C17" t="n">
-        <v>0.128</v>
+        <v>0.1264</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1104</v>
+        <v>-0.0989</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1687</v>
+        <v>1.1539</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1687</v>
+        <v>1.1539</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1687</v>
+        <v>1.1539</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1687</v>
+        <v>1.1539</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1687</v>
+        <v>1.1539</v>
       </c>
       <c r="N17" t="n">
-        <v>211</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.168</v>
+        <v>1.0681</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1279</v>
+        <v>0.117</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1107</v>
+        <v>-0.138</v>
       </c>
       <c r="E18" t="n">
-        <v>1.168</v>
+        <v>1.0681</v>
       </c>
       <c r="F18" t="n">
-        <v>1.168</v>
+        <v>1.0681</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.168</v>
+        <v>1.0681</v>
       </c>
       <c r="I18" t="n">
-        <v>1.168</v>
+        <v>1.0681</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.168</v>
+        <v>1.0681</v>
       </c>
       <c r="N18" t="n">
-        <v>165</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1235</v>
+        <v>1.0543</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1231</v>
+        <v>0.1155</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1308</v>
+        <v>-0.1443</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1235</v>
+        <v>1.0543</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1235</v>
+        <v>1.0543</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1235</v>
+        <v>1.0543</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1235</v>
+        <v>1.0543</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1235</v>
+        <v>1.0543</v>
       </c>
       <c r="N19" t="n">
         <v>165</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9156</v>
+        <v>0.8824</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1003</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2247</v>
+        <v>-0.2225</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9156</v>
+        <v>0.8824</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9156</v>
+        <v>0.8824</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9156</v>
+        <v>0.8824</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9156</v>
+        <v>0.8824</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9156</v>
+        <v>0.8824</v>
       </c>
       <c r="N20" t="n">
         <v>99</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.6763</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0772</v>
+        <v>0.0741</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3197</v>
+        <v>-0.3163</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.6763</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.6763</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.6763</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.6763</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>211</v>
+        <v>159</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.6763</v>
       </c>
       <c r="N21" t="n">
-        <v>211</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6853</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0751</v>
+        <v>0.0712</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3286</v>
+        <v>-0.3284</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6853</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6853</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6853</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6853</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6853</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>159</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4528</v>
+        <v>0.373</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0496</v>
+        <v>0.0409</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4336</v>
+        <v>-0.4544</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4528</v>
+        <v>0.373</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4528</v>
+        <v>0.373</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4528</v>
+        <v>0.373</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4528</v>
+        <v>0.373</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4528</v>
+        <v>0.373</v>
       </c>
       <c r="N23" t="n">
         <v>71</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3862</v>
+        <v>0.3312</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0423</v>
+        <v>0.0363</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4637</v>
+        <v>-0.4734</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3862</v>
+        <v>0.3312</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1066</v>
+        <v>1.0743</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7204</v>
+        <v>-0.7431</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1066</v>
+        <v>1.0743</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1066</v>
+        <v>1.0743</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7204</v>
+        <v>-0.7431</v>
       </c>
       <c r="K24" t="n">
         <v>155</v>
@@ -1541,7 +1541,7 @@
         <v>52</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3862</v>
+        <v>0.3312</v>
       </c>
       <c r="N24" t="n">
         <v>207</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2516</v>
+        <v>0.1783</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0276</v>
+        <v>0.0195</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5244</v>
+        <v>-0.543</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2516</v>
+        <v>0.1783</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2516</v>
+        <v>0.1783</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2516</v>
+        <v>0.1783</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2516</v>
+        <v>0.1783</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2516</v>
+        <v>0.1783</v>
       </c>
       <c r="N25" t="n">
         <v>159</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1261</v>
+        <v>0.1634</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0138</v>
+        <v>0.0179</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.5498</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1261</v>
+        <v>0.1634</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1261</v>
+        <v>0.1634</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1261</v>
+        <v>0.1634</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1261</v>
+        <v>0.1634</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1261</v>
+        <v>0.1634</v>
       </c>
       <c r="N26" t="n">
         <v>194</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0934</v>
+        <v>-0.0438</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0102</v>
+        <v>-0.0048</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6802</v>
+        <v>-0.6441</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0934</v>
+        <v>-0.0438</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.0274</v>
+        <v>-0.9454</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9016</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.0274</v>
+        <v>-0.9454</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.0274</v>
+        <v>-0.9454</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9016</v>
       </c>
       <c r="K27" t="n">
         <v>155</v>
@@ -1679,7 +1679,7 @@
         <v>52</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.09340000000000004</v>
+        <v>-0.04380000000000006</v>
       </c>
       <c r="N27" t="n">
         <v>207</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2334</v>
+        <v>-0.1812</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0256</v>
+        <v>-0.0198</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.7067</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2334</v>
+        <v>-0.1812</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3561</v>
+        <v>0.4362</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.5895</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3561</v>
+        <v>0.4362</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3561</v>
+        <v>0.4362</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.5895</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>155</v>
@@ -1725,7 +1725,7 @@
         <v>52</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2334</v>
+        <v>-0.1812</v>
       </c>
       <c r="N28" t="n">
         <v>207</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2607</v>
+        <v>-0.2898</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0286</v>
+        <v>-0.0317</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7557</v>
+        <v>-0.7561</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2607</v>
+        <v>-0.2898</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2607</v>
+        <v>-0.2898</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2607</v>
+        <v>-0.2898</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2607</v>
+        <v>-0.2898</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2607</v>
+        <v>-0.2898</v>
       </c>
       <c r="N29" t="n">
         <v>194</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PwnAlone</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.35</v>
+        <v>-0.3852</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0383</v>
+        <v>-0.0422</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.796</v>
+        <v>-0.7996</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.35</v>
+        <v>-0.3852</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.35</v>
+        <v>-0.3852</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.35</v>
+        <v>-0.3852</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.35</v>
+        <v>-0.3852</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.35</v>
+        <v>-0.3852</v>
       </c>
       <c r="N30" t="n">
-        <v>71</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>PwnAlone</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3582</v>
+        <v>-0.4009</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0392</v>
+        <v>-0.0439</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7997</v>
+        <v>-0.8067</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3582</v>
+        <v>-0.4009</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3582</v>
+        <v>-0.4009</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3582</v>
+        <v>-0.4009</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3582</v>
+        <v>-0.4009</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3582</v>
+        <v>-0.4009</v>
       </c>
       <c r="N31" t="n">
-        <v>112</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5607</v>
+        <v>-0.6199</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0614</v>
+        <v>-0.0679</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8911</v>
+        <v>-0.9064</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5607</v>
+        <v>-0.6199</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5607</v>
+        <v>-0.6199</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5607</v>
+        <v>-0.6199</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5607</v>
+        <v>-0.6199</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5607</v>
+        <v>-0.6199</v>
       </c>
       <c r="N32" t="n">
         <v>71</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6388</v>
+        <v>-0.7066</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0774</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9264</v>
+        <v>-0.9459</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6388</v>
+        <v>-0.7066</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6388</v>
+        <v>-0.7066</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6388</v>
+        <v>-0.7066</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6388</v>
+        <v>-0.7066</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6388</v>
+        <v>-0.7066</v>
       </c>
       <c r="N33" t="n">
-        <v>211</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6855</v>
+        <v>-0.7086</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0751</v>
+        <v>-0.0776</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9475</v>
+        <v>-0.9468</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6855</v>
+        <v>-0.7086</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6855</v>
+        <v>-0.7086</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6855</v>
+        <v>-0.7086</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6855</v>
+        <v>-0.7086</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6855</v>
+        <v>-0.7086</v>
       </c>
       <c r="N34" t="n">
-        <v>165</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7097</v>
+        <v>-0.7605</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0833</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9584</v>
+        <v>-0.9704</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7097</v>
+        <v>-0.7605</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7097</v>
+        <v>-0.7605</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7097</v>
+        <v>-0.7605</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7097</v>
+        <v>-0.7605</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7097</v>
+        <v>-0.7605</v>
       </c>
       <c r="N35" t="n">
         <v>71</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8429</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0185</v>
+        <v>-1.0255</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8429</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8429</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8429</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8429</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8429</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>69</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9044</v>
+        <v>-0.9366</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1026</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0463</v>
+        <v>-1.0506</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9044</v>
+        <v>-0.9366</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9044</v>
+        <v>-0.9366</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9044</v>
+        <v>-0.9366</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9044</v>
+        <v>-0.9366</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9044</v>
+        <v>-0.9366</v>
       </c>
       <c r="N37" t="n">
         <v>165</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9308</v>
+        <v>-0.9694</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.102</v>
+        <v>-0.1062</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0582</v>
+        <v>-1.0655</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9308</v>
+        <v>-0.9694</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9308</v>
+        <v>-0.9694</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9308</v>
+        <v>-0.9694</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9308</v>
+        <v>-0.9694</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9308</v>
+        <v>-0.9694</v>
       </c>
       <c r="N38" t="n">
         <v>69</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0695</v>
+        <v>-1.1117</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1172</v>
+        <v>-0.1218</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1208</v>
+        <v>-1.1303</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0695</v>
+        <v>-1.1117</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0695</v>
+        <v>-1.1117</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0695</v>
+        <v>-1.1117</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0695</v>
+        <v>-1.1117</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0695</v>
+        <v>-1.1117</v>
       </c>
       <c r="N39" t="n">
         <v>69</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1439</v>
+        <v>-1.1812</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1253</v>
+        <v>-0.1294</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1544</v>
+        <v>-1.1619</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1439</v>
+        <v>-1.1812</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.1439</v>
+        <v>-1.1812</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.1439</v>
+        <v>-1.1812</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1439</v>
+        <v>-1.1812</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1439</v>
+        <v>-1.1812</v>
       </c>
       <c r="N40" t="n">
         <v>69</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4341</v>
+        <v>-1.4636</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1571</v>
+        <v>-0.1603</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2854</v>
+        <v>-1.2905</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4341</v>
+        <v>-1.4636</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4341</v>
+        <v>-1.4636</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4341</v>
+        <v>-1.4636</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4341</v>
+        <v>-1.4636</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4341</v>
+        <v>-1.4636</v>
       </c>
       <c r="N41" t="n">
         <v>71</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-1.6511</v>
+        <v>-1.6295</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.1809</v>
+        <v>-0.1785</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.3834</v>
+        <v>-1.366</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.6511</v>
+        <v>-1.6295</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.6511</v>
+        <v>-1.6295</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.6511</v>
+        <v>-1.6295</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.6511</v>
+        <v>-1.6295</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-1.6511</v>
+        <v>-1.6295</v>
       </c>
       <c r="N42" t="n">
         <v>159</v>
@@ -2475,10 +2475,10 @@
         <v>1.35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7343</v>
+        <v>0.6983</v>
       </c>
       <c r="J2" t="n">
-        <v>18.3575</v>
+        <v>17.4575</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0123</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3075</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.18</v>
+        <v>-0.1953</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.5</v>
+        <v>-4.8825</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.76</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2704</v>
+        <v>-0.285</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.76</v>
+        <v>-7.125</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3282</v>
+        <v>-0.3414</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.205</v>
+        <v>-8.535</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0714</v>
+        <v>1.0357</v>
       </c>
       <c r="J7" t="n">
-        <v>26.785</v>
+        <v>25.8925</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.44</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0714</v>
+        <v>1.0357</v>
       </c>
       <c r="J8" t="n">
-        <v>26.785</v>
+        <v>25.8925</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4176</v>
+        <v>0.4144</v>
       </c>
       <c r="J9" t="n">
-        <v>10.44</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>0.99</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0954</v>
+        <v>-0.0877</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.385</v>
+        <v>-2.1925</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>0.83</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5888</v>
+        <v>-0.5498</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.72</v>
+        <v>-13.745</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.21</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4796</v>
+        <v>0.4672</v>
       </c>
       <c r="J12" t="n">
-        <v>12.9492</v>
+        <v>12.6144</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>1.07</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1997</v>
+        <v>0.2033</v>
       </c>
       <c r="J13" t="n">
-        <v>5.3919</v>
+        <v>5.4891</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>1.07</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1997</v>
+        <v>0.2033</v>
       </c>
       <c r="J14" t="n">
-        <v>5.3919</v>
+        <v>5.4891</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.77</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2613</v>
+        <v>-0.276</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.0551</v>
+        <v>-7.452</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.57</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.45</v>
+        <v>-0.4581</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.15</v>
+        <v>-12.3687</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.55</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2132</v>
+        <v>1.2415</v>
       </c>
       <c r="J17" t="n">
-        <v>32.7564</v>
+        <v>33.5205</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.33</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8718</v>
+        <v>0.8198</v>
       </c>
       <c r="J18" t="n">
-        <v>23.5386</v>
+        <v>22.1346</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2811</v>
+        <v>0.2887</v>
       </c>
       <c r="J19" t="n">
-        <v>7.5897</v>
+        <v>7.7949</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.275</v>
+        <v>-0.2624</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.425</v>
+        <v>-7.0848</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.275</v>
+        <v>-0.2624</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.425</v>
+        <v>-7.0848</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0291</v>
+        <v>0.9674</v>
       </c>
       <c r="J22" t="n">
-        <v>34.9894</v>
+        <v>32.8916</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.23</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6692</v>
+        <v>0.6353</v>
       </c>
       <c r="J23" t="n">
-        <v>22.7528</v>
+        <v>21.6002</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1103</v>
+        <v>-0.1109</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.7502</v>
+        <v>-3.7706</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>0.92</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3093</v>
+        <v>-0.301</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.5162</v>
+        <v>-10.234</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.82</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5886</v>
+        <v>-0.5547</v>
       </c>
       <c r="J26" t="n">
-        <v>-20.0124</v>
+        <v>-18.8598</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.08</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2114</v>
+        <v>0.2171</v>
       </c>
       <c r="J27" t="n">
-        <v>7.1876</v>
+        <v>7.3814</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.145</v>
+        <v>0.152</v>
       </c>
       <c r="J28" t="n">
-        <v>4.93</v>
+        <v>5.168</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>0.93</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0974</v>
+        <v>-0.1095</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.3116</v>
+        <v>-3.723</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1202</v>
+        <v>-0.1332</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.0868</v>
+        <v>-4.5288</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.9</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1314</v>
+        <v>-0.1447</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.4676</v>
+        <v>-4.9198</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8232</v>
+        <v>0.7736</v>
       </c>
       <c r="J32" t="n">
-        <v>21.4032</v>
+        <v>20.1136</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5044</v>
+        <v>0.4909</v>
       </c>
       <c r="J33" t="n">
-        <v>13.1144</v>
+        <v>12.7634</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.14</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4271</v>
+        <v>0.4207</v>
       </c>
       <c r="J34" t="n">
-        <v>11.1046</v>
+        <v>10.9382</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>0.99</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0803</v>
+        <v>-0.0772</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.0878</v>
+        <v>-2.0072</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2269</v>
+        <v>-0.2208</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.8994</v>
+        <v>-5.7408</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.444</v>
+        <v>0.4376</v>
       </c>
       <c r="J37" t="n">
-        <v>11.544</v>
+        <v>11.3776</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2505</v>
+        <v>0.2555</v>
       </c>
       <c r="J38" t="n">
-        <v>6.513</v>
+        <v>6.643</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1653</v>
+        <v>0.1727</v>
       </c>
       <c r="J39" t="n">
-        <v>4.2978</v>
+        <v>4.4902</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.217</v>
+        <v>-0.2309</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.642</v>
+        <v>-6.0034</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2961</v>
+        <v>-0.309</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.6986</v>
+        <v>-8.034000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>0.76</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.233</v>
+        <v>-0.2562</v>
       </c>
       <c r="J42" t="n">
-        <v>-5.359</v>
+        <v>-5.8926</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>0.73</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2633</v>
+        <v>-0.2855</v>
       </c>
       <c r="J43" t="n">
-        <v>-6.0559</v>
+        <v>-6.5665</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>0.68</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3111</v>
+        <v>-0.3318</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.1553</v>
+        <v>-7.6314</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>0.62</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3645</v>
+        <v>-0.3834</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.3835</v>
+        <v>-8.818199999999999</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>0.52</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4576</v>
+        <v>-0.4714</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.5248</v>
+        <v>-10.8422</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3048</v>
+        <v>1.2851</v>
       </c>
       <c r="J47" t="n">
-        <v>30.0104</v>
+        <v>29.5573</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>1.49</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0988</v>
+        <v>1.0639</v>
       </c>
       <c r="J48" t="n">
-        <v>25.2724</v>
+        <v>24.4697</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>1.33</v>
       </c>
       <c r="I49" t="n">
-        <v>0.831</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>19.113</v>
+        <v>18.2114</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>1.2</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5304</v>
+        <v>0.5248</v>
       </c>
       <c r="J50" t="n">
-        <v>12.1992</v>
+        <v>12.0704</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>1.08</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2092</v>
+        <v>0.2318</v>
       </c>
       <c r="J51" t="n">
-        <v>4.8116</v>
+        <v>5.3314</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.16</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3689</v>
+        <v>0.3676</v>
       </c>
       <c r="J52" t="n">
-        <v>10.6981</v>
+        <v>10.6604</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3303</v>
+        <v>0.3314</v>
       </c>
       <c r="J53" t="n">
-        <v>9.5787</v>
+        <v>9.6106</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>0.99</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0197</v>
+        <v>-0.0246</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.5713</v>
+        <v>-0.7134</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.91</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1213</v>
+        <v>-0.1341</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.5177</v>
+        <v>-3.8889</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.72</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3154</v>
+        <v>-0.3277</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.146599999999999</v>
+        <v>-9.503299999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.4</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0292</v>
+        <v>0.9707</v>
       </c>
       <c r="J57" t="n">
-        <v>29.8468</v>
+        <v>28.1503</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.15</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4517</v>
+        <v>0.4434</v>
       </c>
       <c r="J58" t="n">
-        <v>13.0993</v>
+        <v>12.8586</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>1.12</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3738</v>
+        <v>0.372</v>
       </c>
       <c r="J59" t="n">
-        <v>10.8402</v>
+        <v>10.788</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>1.07</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2348</v>
+        <v>0.2424</v>
       </c>
       <c r="J60" t="n">
-        <v>6.8092</v>
+        <v>7.0296</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5486</v>
+        <v>-0.5163</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.9094</v>
+        <v>-14.9727</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.68</v>
       </c>
       <c r="I62" t="n">
-        <v>1.342</v>
+        <v>1.3222</v>
       </c>
       <c r="J62" t="n">
-        <v>32.208</v>
+        <v>31.7328</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.48</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0961</v>
+        <v>1.0588</v>
       </c>
       <c r="J63" t="n">
-        <v>26.3064</v>
+        <v>25.4112</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>1.26</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6604</v>
       </c>
       <c r="J64" t="n">
-        <v>16.44</v>
+        <v>15.8496</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>1.06</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1616</v>
+        <v>0.1839</v>
       </c>
       <c r="J65" t="n">
-        <v>3.8784</v>
+        <v>4.4136</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.99</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1264</v>
+        <v>-0.1094</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.0336</v>
+        <v>-2.6256</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.16</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4516</v>
+        <v>0.4285</v>
       </c>
       <c r="J67" t="n">
-        <v>10.8384</v>
+        <v>10.284</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.12</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3677</v>
+        <v>0.3505</v>
       </c>
       <c r="J68" t="n">
-        <v>8.8248</v>
+        <v>8.412000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1331</v>
+        <v>-0.1516</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.1944</v>
+        <v>-3.6384</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.45</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.5482</v>
       </c>
       <c r="J70" t="n">
-        <v>-13.0272</v>
+        <v>-13.1568</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.37</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6157</v>
+        <v>-0.6161</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.7768</v>
+        <v>-14.7864</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>0.92</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.1092</v>
       </c>
       <c r="J72" t="n">
-        <v>-2.1344</v>
+        <v>-2.5116</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>0.91</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1045</v>
+        <v>-0.1213</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.4035</v>
+        <v>-2.7899</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>0.87</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1488</v>
+        <v>-0.1664</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.4224</v>
+        <v>-3.8272</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>0.72</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2954</v>
+        <v>-0.3121</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.7942</v>
+        <v>-7.1783</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2954</v>
+        <v>-0.3121</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.7942</v>
+        <v>-7.1783</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.79</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9176</v>
+        <v>0.8985</v>
       </c>
       <c r="J77" t="n">
-        <v>21.1048</v>
+        <v>20.6655</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.54</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6577</v>
       </c>
       <c r="J78" t="n">
-        <v>15.1064</v>
+        <v>15.1271</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>1.16</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2273</v>
+        <v>0.2466</v>
       </c>
       <c r="J79" t="n">
-        <v>5.2279</v>
+        <v>5.6718</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.89</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.171</v>
+        <v>-0.1783</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.933</v>
+        <v>-4.1009</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.87</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1926</v>
+        <v>-0.2003</v>
       </c>
       <c r="J81" t="n">
-        <v>-4.4298</v>
+        <v>-4.6069</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.93</v>
       </c>
       <c r="I82" t="n">
-        <v>1.5848</v>
+        <v>1.5863</v>
       </c>
       <c r="J82" t="n">
-        <v>31.696</v>
+        <v>31.726</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.93</v>
       </c>
       <c r="I83" t="n">
-        <v>1.5848</v>
+        <v>1.5863</v>
       </c>
       <c r="J83" t="n">
-        <v>31.696</v>
+        <v>31.726</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1.64</v>
       </c>
       <c r="I84" t="n">
-        <v>1.2557</v>
+        <v>1.2376</v>
       </c>
       <c r="J84" t="n">
-        <v>25.114</v>
+        <v>24.752</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>1.03</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0174</v>
+        <v>0.0571</v>
       </c>
       <c r="J85" t="n">
-        <v>0.348</v>
+        <v>1.142</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.98</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.211</v>
+        <v>-0.1815</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.22</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>0.77</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.202</v>
+        <v>-0.2299</v>
       </c>
       <c r="J87" t="n">
-        <v>-4.04</v>
+        <v>-4.598</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>0.7</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2765</v>
+        <v>-0.3014</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.53</v>
+        <v>-6.028</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>0.61</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3641</v>
+        <v>-0.3848</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.282</v>
+        <v>-7.696</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.54</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4261</v>
+        <v>-0.4439</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.522</v>
+        <v>-8.878</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.34</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6162</v>
+        <v>-0.6202</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.324</v>
+        <v>-12.404</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.41</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0323</v>
+        <v>0.9771</v>
       </c>
       <c r="J92" t="n">
-        <v>25.8075</v>
+        <v>24.4275</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.33</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8759</v>
+        <v>0.8227</v>
       </c>
       <c r="J93" t="n">
-        <v>21.8975</v>
+        <v>20.5675</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2548</v>
+        <v>0.2636</v>
       </c>
       <c r="J94" t="n">
-        <v>6.37</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>1.04</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1297</v>
+        <v>0.1451</v>
       </c>
       <c r="J95" t="n">
-        <v>3.2425</v>
+        <v>3.6275</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.93</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3032</v>
+        <v>-0.2896</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.58</v>
+        <v>-7.24</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.32</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6651</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="J97" t="n">
-        <v>16.6275</v>
+        <v>15.965</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>1.14</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3352</v>
+        <v>0.335</v>
       </c>
       <c r="J98" t="n">
-        <v>8.380000000000001</v>
+        <v>8.375</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>1.13</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3155</v>
+        <v>0.3164</v>
       </c>
       <c r="J99" t="n">
-        <v>7.8875</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>0.65</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3796</v>
+        <v>-0.3902</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.49</v>
+        <v>-9.755000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.6</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4258</v>
+        <v>-0.4345</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.645</v>
+        <v>-10.8625</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.57</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2365</v>
+        <v>1.2048</v>
       </c>
       <c r="J102" t="n">
-        <v>30.9125</v>
+        <v>30.12</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.15</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4414</v>
+        <v>0.4366</v>
       </c>
       <c r="J103" t="n">
-        <v>11.035</v>
+        <v>10.915</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>1.13</v>
       </c>
       <c r="I104" t="n">
-        <v>0.3894</v>
+        <v>0.389</v>
       </c>
       <c r="J104" t="n">
-        <v>9.734999999999999</v>
+        <v>9.725</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>1.1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3076</v>
+        <v>0.3138</v>
       </c>
       <c r="J105" t="n">
-        <v>7.69</v>
+        <v>7.845</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2771</v>
+        <v>-0.2639</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.9275</v>
+        <v>-6.5975</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.14</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3855</v>
+        <v>0.3719</v>
       </c>
       <c r="J107" t="n">
-        <v>9.637499999999999</v>
+        <v>9.297499999999999</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>0.84</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1807</v>
+        <v>-0.1983</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.5175</v>
+        <v>-4.9575</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>0.82</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2001</v>
+        <v>-0.2179</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.0025</v>
+        <v>-5.4475</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2099</v>
+        <v>-0.2277</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.2475</v>
+        <v>-5.6925</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.6</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4106</v>
+        <v>-0.4225</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.265</v>
+        <v>-10.5625</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.55</v>
       </c>
       <c r="I112" t="n">
-        <v>1.2111</v>
+        <v>1.1777</v>
       </c>
       <c r="J112" t="n">
-        <v>36.333</v>
+        <v>35.331</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.37</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9565</v>
+        <v>0.8973</v>
       </c>
       <c r="J113" t="n">
-        <v>28.695</v>
+        <v>26.919</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.36</v>
       </c>
       <c r="I114" t="n">
-        <v>0.9359</v>
+        <v>0.8776</v>
       </c>
       <c r="J114" t="n">
-        <v>28.077</v>
+        <v>26.328</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>0.85</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5377</v>
+        <v>-0.5034</v>
       </c>
       <c r="J115" t="n">
-        <v>-16.131</v>
+        <v>-15.102</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.76</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7716</v>
+        <v>-0.7118</v>
       </c>
       <c r="J116" t="n">
-        <v>-23.148</v>
+        <v>-21.354</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.15</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3763</v>
+        <v>0.3692</v>
       </c>
       <c r="J117" t="n">
-        <v>11.289</v>
+        <v>11.076</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.09</v>
       </c>
       <c r="I118" t="n">
-        <v>0.253</v>
+        <v>0.2525</v>
       </c>
       <c r="J118" t="n">
-        <v>7.59</v>
+        <v>7.575</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.91</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1143</v>
+        <v>-0.1287</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.429</v>
+        <v>-3.861</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.9</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1248</v>
+        <v>-0.1397</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.744</v>
+        <v>-4.191</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.49</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5193</v>
+        <v>-0.5243</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.579</v>
+        <v>-15.729</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8822</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="J122" t="n">
-        <v>25.5838</v>
+        <v>23.8699</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.24</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6887</v>
+        <v>0.6535</v>
       </c>
       <c r="J123" t="n">
-        <v>19.9723</v>
+        <v>18.9515</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>1.05</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1806</v>
+        <v>0.189</v>
       </c>
       <c r="J124" t="n">
-        <v>5.2374</v>
+        <v>5.481</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>0.9</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3722</v>
+        <v>-0.3582</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.7938</v>
+        <v>-10.3878</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.9</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3722</v>
+        <v>-0.3582</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.7938</v>
+        <v>-10.3878</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.24</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5447</v>
+        <v>0.5253</v>
       </c>
       <c r="J127" t="n">
-        <v>15.7963</v>
+        <v>15.2337</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>0.91</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1147</v>
+        <v>-0.129</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.3263</v>
+        <v>-3.741</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>0.89</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1362</v>
+        <v>-0.1512</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.9498</v>
+        <v>-4.3848</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.86</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1678</v>
+        <v>-0.1834</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.8662</v>
+        <v>-5.3186</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3452</v>
+        <v>-0.3582</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.0108</v>
+        <v>-10.3878</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.56</v>
       </c>
       <c r="I132" t="n">
-        <v>1.2603</v>
+        <v>1.2236</v>
       </c>
       <c r="J132" t="n">
-        <v>37.809</v>
+        <v>36.708</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>1.04</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1516</v>
+        <v>0.1602</v>
       </c>
       <c r="J133" t="n">
-        <v>4.548</v>
+        <v>4.806</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>1.01</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0403</v>
+        <v>0.0498</v>
       </c>
       <c r="J134" t="n">
-        <v>1.209</v>
+        <v>1.494</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.98</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1098</v>
+        <v>-0.1105</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.294</v>
+        <v>-3.315</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.74</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7932</v>
+        <v>-0.7357</v>
       </c>
       <c r="J136" t="n">
-        <v>-23.796</v>
+        <v>-22.071</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.37</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7197</v>
+        <v>0.6929</v>
       </c>
       <c r="J137" t="n">
-        <v>21.591</v>
+        <v>20.787</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1539</v>
+        <v>0.1645</v>
       </c>
       <c r="J138" t="n">
-        <v>4.617</v>
+        <v>4.935</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0034</v>
+        <v>-0.0026</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.102</v>
+        <v>-0.078</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.96</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0759</v>
       </c>
       <c r="J140" t="n">
-        <v>-2.028</v>
+        <v>-2.277</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.83</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2137</v>
+        <v>-0.2261</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.411</v>
+        <v>-6.783</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.52</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8359</v>
+        <v>0.7884</v>
       </c>
       <c r="J142" t="n">
-        <v>18.3898</v>
+        <v>17.3448</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.73</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2869</v>
+        <v>-0.3036</v>
       </c>
       <c r="J143" t="n">
-        <v>-6.3118</v>
+        <v>-6.6792</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.71</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3061</v>
+        <v>-0.3223</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.7342</v>
+        <v>-7.0906</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.66</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3535</v>
+        <v>-0.3681</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.777</v>
+        <v>-8.0982</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4469</v>
+        <v>-0.4571</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.831799999999999</v>
+        <v>-10.0562</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.6</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7185</v>
+        <v>0.7153</v>
       </c>
       <c r="J147" t="n">
-        <v>15.807</v>
+        <v>15.7366</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4479</v>
+        <v>0.4614</v>
       </c>
       <c r="J148" t="n">
-        <v>9.8538</v>
+        <v>10.1508</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.24</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3243</v>
+        <v>0.342</v>
       </c>
       <c r="J149" t="n">
-        <v>7.1346</v>
+        <v>7.524</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.22</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3007</v>
+        <v>0.319</v>
       </c>
       <c r="J150" t="n">
-        <v>6.6154</v>
+        <v>7.018</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.89</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1719</v>
+        <v>-0.179</v>
       </c>
       <c r="J151" t="n">
-        <v>-3.7818</v>
+        <v>-3.938</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.35</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9735</v>
+        <v>0.9034</v>
       </c>
       <c r="J152" t="n">
-        <v>28.2315</v>
+        <v>26.1986</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.16</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5044</v>
+        <v>0.4854</v>
       </c>
       <c r="J153" t="n">
-        <v>14.6276</v>
+        <v>14.0766</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4777</v>
+        <v>0.4614</v>
       </c>
       <c r="J154" t="n">
-        <v>13.8533</v>
+        <v>13.3806</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.87</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4419</v>
+        <v>-0.4251</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.8151</v>
+        <v>-12.3279</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.0991</v>
+        <v>-1.0023</v>
       </c>
       <c r="J156" t="n">
-        <v>-31.8739</v>
+        <v>-29.0667</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.51</v>
       </c>
       <c r="I157" t="n">
-        <v>0.969</v>
+        <v>0.9165</v>
       </c>
       <c r="J157" t="n">
-        <v>28.101</v>
+        <v>26.5785</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.23</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4968</v>
+        <v>0.4867</v>
       </c>
       <c r="J158" t="n">
-        <v>14.4072</v>
+        <v>14.1143</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>1.16</v>
       </c>
       <c r="I159" t="n">
-        <v>0.367</v>
+        <v>0.3663</v>
       </c>
       <c r="J159" t="n">
-        <v>10.643</v>
+        <v>10.6227</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>0.63</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4006</v>
+        <v>-0.41</v>
       </c>
       <c r="J160" t="n">
-        <v>-11.6174</v>
+        <v>-11.89</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.42</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5891999999999999</v>
+        <v>-0.5888</v>
       </c>
       <c r="J161" t="n">
-        <v>-17.0868</v>
+        <v>-17.0752</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.45</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5533</v>
+        <v>0.5621</v>
       </c>
       <c r="J162" t="n">
-        <v>12.7259</v>
+        <v>12.9283</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.31</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4003</v>
+        <v>0.4164</v>
       </c>
       <c r="J163" t="n">
-        <v>9.206899999999999</v>
+        <v>9.577199999999999</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.27</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3562</v>
+        <v>0.3737</v>
       </c>
       <c r="J164" t="n">
-        <v>8.192600000000001</v>
+        <v>8.5951</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.22</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2978</v>
+        <v>0.3168</v>
       </c>
       <c r="J165" t="n">
-        <v>6.8494</v>
+        <v>7.2864</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>1.2</v>
       </c>
       <c r="I166" t="n">
-        <v>0.2734</v>
+        <v>0.293</v>
       </c>
       <c r="J166" t="n">
-        <v>6.2882</v>
+        <v>6.739</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>0.85</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.1504</v>
+        <v>-0.1725</v>
       </c>
       <c r="J167" t="n">
-        <v>-3.4592</v>
+        <v>-3.9675</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>0.79</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2141</v>
+        <v>-0.2354</v>
       </c>
       <c r="J168" t="n">
-        <v>-4.9243</v>
+        <v>-5.4142</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.75</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2537</v>
+        <v>-0.2742</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.8351</v>
+        <v>-6.3066</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3084</v>
+        <v>-0.3277</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.0932</v>
+        <v>-7.5371</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.51</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4763</v>
+        <v>-0.4875</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.9549</v>
+        <v>-11.2125</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.3</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6069</v>
+        <v>0.5898</v>
       </c>
       <c r="J172" t="n">
-        <v>16.3863</v>
+        <v>15.9246</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.24</v>
       </c>
       <c r="I173" t="n">
-        <v>0.502</v>
+        <v>0.4939</v>
       </c>
       <c r="J173" t="n">
-        <v>13.554</v>
+        <v>13.3353</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>1.13</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2991</v>
+        <v>0.3044</v>
       </c>
       <c r="J174" t="n">
-        <v>8.075699999999999</v>
+        <v>8.2188</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1593</v>
+        <v>-0.1718</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.3011</v>
+        <v>-4.6386</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.59</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4411</v>
+        <v>-0.4481</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.9097</v>
+        <v>-12.0987</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.43</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0913</v>
+        <v>1.0408</v>
       </c>
       <c r="J177" t="n">
-        <v>29.4651</v>
+        <v>28.1016</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0777</v>
+        <v>1.0248</v>
       </c>
       <c r="J178" t="n">
-        <v>29.0979</v>
+        <v>27.6696</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.86</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.4764</v>
+        <v>-0.4549</v>
       </c>
       <c r="J179" t="n">
-        <v>-12.8628</v>
+        <v>-12.2823</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.6103</v>
+        <v>-0.575</v>
       </c>
       <c r="J180" t="n">
-        <v>-16.4781</v>
+        <v>-15.525</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.74</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7893</v>
+        <v>-0.7329</v>
       </c>
       <c r="J181" t="n">
-        <v>-21.3111</v>
+        <v>-19.7883</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.18</v>
       </c>
       <c r="I182" t="n">
-        <v>0.463</v>
+        <v>0.4444</v>
       </c>
       <c r="J182" t="n">
-        <v>12.038</v>
+        <v>11.5544</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>0.95</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0592</v>
+        <v>-0.0733</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.5392</v>
+        <v>-1.9058</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>0.91</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1076</v>
+        <v>-0.1236</v>
       </c>
       <c r="J184" t="n">
-        <v>-2.7976</v>
+        <v>-3.2136</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>0.64</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.374</v>
+        <v>-0.3874</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.724</v>
+        <v>-10.0724</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4484</v>
+        <v>-0.4583</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.6584</v>
+        <v>-11.9158</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.51</v>
       </c>
       <c r="I187" t="n">
-        <v>1.131</v>
+        <v>1.0975</v>
       </c>
       <c r="J187" t="n">
-        <v>29.406</v>
+        <v>28.535</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.5</v>
       </c>
       <c r="I188" t="n">
-        <v>1.1186</v>
+        <v>1.0841</v>
       </c>
       <c r="J188" t="n">
-        <v>29.0836</v>
+        <v>28.1866</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>1.23</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.5962</v>
       </c>
       <c r="J189" t="n">
-        <v>15.9224</v>
+        <v>15.5012</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.5399</v>
+        <v>0.5313</v>
       </c>
       <c r="J190" t="n">
-        <v>14.0374</v>
+        <v>13.8138</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>1.1</v>
       </c>
       <c r="I191" t="n">
-        <v>0.2772</v>
+        <v>0.2926</v>
       </c>
       <c r="J191" t="n">
-        <v>7.2072</v>
+        <v>7.6076</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.16</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4457</v>
+        <v>0.4242</v>
       </c>
       <c r="J192" t="n">
-        <v>11.1425</v>
+        <v>10.605</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>0.9</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1123</v>
+        <v>-0.1301</v>
       </c>
       <c r="J193" t="n">
-        <v>-2.8075</v>
+        <v>-3.2525</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>0.87</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1457</v>
+        <v>-0.1639</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.6425</v>
+        <v>-4.0975</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.6</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4056</v>
+        <v>-0.4186</v>
       </c>
       <c r="J195" t="n">
-        <v>-10.14</v>
+        <v>-10.465</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>0.5</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4982</v>
+        <v>-0.5062</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.455</v>
+        <v>-12.655</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.69</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3628</v>
+        <v>1.3428</v>
       </c>
       <c r="J197" t="n">
-        <v>34.07</v>
+        <v>33.57</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.47</v>
       </c>
       <c r="I198" t="n">
-        <v>1.09</v>
+        <v>1.0505</v>
       </c>
       <c r="J198" t="n">
-        <v>27.25</v>
+        <v>26.2625</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>1.2</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5383</v>
       </c>
       <c r="J199" t="n">
-        <v>13.7475</v>
+        <v>13.4575</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>1.03</v>
       </c>
       <c r="I200" t="n">
-        <v>0.0698</v>
+        <v>0.0939</v>
       </c>
       <c r="J200" t="n">
-        <v>1.745</v>
+        <v>2.3475</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3888</v>
+        <v>-0.3634</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.720000000000001</v>
+        <v>-9.085000000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1.56</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1099</v>
+        <v>1.0641</v>
       </c>
       <c r="J202" t="n">
-        <v>26.6376</v>
+        <v>25.5384</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.78</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2352</v>
+        <v>-0.2537</v>
       </c>
       <c r="J203" t="n">
-        <v>-5.6448</v>
+        <v>-6.0888</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.59</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.4152</v>
+        <v>-0.4277</v>
       </c>
       <c r="J204" t="n">
-        <v>-9.9648</v>
+        <v>-10.2648</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.57</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4338</v>
+        <v>-0.4454</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.4112</v>
+        <v>-10.6896</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.54</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4616</v>
+        <v>-0.4717</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.0784</v>
+        <v>-11.3208</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.85</v>
       </c>
       <c r="I207" t="n">
-        <v>1.5521</v>
+        <v>1.5424</v>
       </c>
       <c r="J207" t="n">
-        <v>37.2504</v>
+        <v>37.0176</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.29</v>
       </c>
       <c r="I208" t="n">
-        <v>0.755</v>
+        <v>0.7221</v>
       </c>
       <c r="J208" t="n">
-        <v>18.12</v>
+        <v>17.3304</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>1.2</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.5369</v>
       </c>
       <c r="J209" t="n">
-        <v>13.1496</v>
+        <v>12.8856</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>1.11</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3141</v>
+        <v>0.3247</v>
       </c>
       <c r="J210" t="n">
-        <v>7.5384</v>
+        <v>7.7928</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.9</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4203</v>
+        <v>-0.3919</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.0872</v>
+        <v>-9.4056</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.38</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0394</v>
+        <v>0.9741</v>
       </c>
       <c r="J212" t="n">
-        <v>28.0638</v>
+        <v>26.3007</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>1.13</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4344</v>
+        <v>0.4199</v>
       </c>
       <c r="J213" t="n">
-        <v>11.7288</v>
+        <v>11.3373</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2594</v>
+        <v>-0.2591</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.0038</v>
+        <v>-6.9957</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.78</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.6722</v>
+        <v>-0.6328</v>
       </c>
       <c r="J215" t="n">
-        <v>-18.1494</v>
+        <v>-17.0856</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.77</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6978</v>
+        <v>-0.6553</v>
       </c>
       <c r="J216" t="n">
-        <v>-18.8406</v>
+        <v>-17.6931</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.75</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1904</v>
+        <v>1.1685</v>
       </c>
       <c r="J217" t="n">
-        <v>32.1408</v>
+        <v>31.5495</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>0.98</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0404</v>
+        <v>-0.0461</v>
       </c>
       <c r="J218" t="n">
-        <v>-1.0908</v>
+        <v>-1.2447</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>0.95</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0808</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.1816</v>
+        <v>-2.4273</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>0.86</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1829</v>
+        <v>-0.1951</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.9383</v>
+        <v>-5.2677</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3415</v>
+        <v>-0.3518</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.220499999999999</v>
+        <v>-9.4986</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.8</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4335</v>
+        <v>1.4278</v>
       </c>
       <c r="J222" t="n">
-        <v>27.2365</v>
+        <v>27.1282</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>1.78</v>
       </c>
       <c r="I223" t="n">
-        <v>1.411</v>
+        <v>1.4039</v>
       </c>
       <c r="J223" t="n">
-        <v>26.809</v>
+        <v>26.6741</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>1.67</v>
       </c>
       <c r="I224" t="n">
-        <v>1.2861</v>
+        <v>1.271</v>
       </c>
       <c r="J224" t="n">
-        <v>24.4359</v>
+        <v>24.149</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>1.44</v>
       </c>
       <c r="I225" t="n">
-        <v>1.0155</v>
+        <v>0.9721</v>
       </c>
       <c r="J225" t="n">
-        <v>19.2945</v>
+        <v>18.4699</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.97</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2536</v>
+        <v>-0.2219</v>
       </c>
       <c r="J226" t="n">
-        <v>-4.8184</v>
+        <v>-4.2161</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>0.97</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1146</v>
+        <v>0.0519</v>
       </c>
       <c r="J227" t="n">
-        <v>2.1774</v>
+        <v>0.9861</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>0.52</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.4408</v>
+        <v>-0.4584</v>
       </c>
       <c r="J228" t="n">
-        <v>-8.3752</v>
+        <v>-8.7096</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>0.49</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.4688</v>
+        <v>-0.4846</v>
       </c>
       <c r="J229" t="n">
-        <v>-8.9072</v>
+        <v>-9.2074</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.44</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5163</v>
+        <v>-0.5286</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.809699999999999</v>
+        <v>-10.0434</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.44</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5163</v>
+        <v>-0.5286</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.809699999999999</v>
+        <v>-10.0434</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>1.47</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1557</v>
+        <v>1.1095</v>
       </c>
       <c r="J232" t="n">
-        <v>32.3596</v>
+        <v>31.066</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>1.08</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2828</v>
+        <v>0.2826</v>
       </c>
       <c r="J233" t="n">
-        <v>7.9184</v>
+        <v>7.9128</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>1.06</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2224</v>
+        <v>0.2259</v>
       </c>
       <c r="J234" t="n">
-        <v>6.2272</v>
+        <v>6.3252</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>0.77</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.7056</v>
+        <v>-0.6607</v>
       </c>
       <c r="J235" t="n">
-        <v>-19.7568</v>
+        <v>-18.4996</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.74</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7814</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="J236" t="n">
-        <v>-21.8792</v>
+        <v>-20.3644</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.24</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5033</v>
+        <v>0.4948</v>
       </c>
       <c r="J237" t="n">
-        <v>14.0924</v>
+        <v>13.8544</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.17</v>
       </c>
       <c r="I238" t="n">
-        <v>0.376</v>
+        <v>0.3768</v>
       </c>
       <c r="J238" t="n">
-        <v>10.528</v>
+        <v>10.5504</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>1.06</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1571</v>
+        <v>0.1668</v>
       </c>
       <c r="J239" t="n">
-        <v>4.3988</v>
+        <v>4.6704</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>0.87</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1696</v>
+        <v>-0.1823</v>
       </c>
       <c r="J240" t="n">
-        <v>-4.7488</v>
+        <v>-5.1044</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.78</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2617</v>
+        <v>-0.2742</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.3276</v>
+        <v>-7.6776</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>2.06</v>
       </c>
       <c r="I242" t="n">
-        <v>1.772</v>
+        <v>1.7754</v>
       </c>
       <c r="J242" t="n">
-        <v>38.984</v>
+        <v>39.0588</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.44</v>
       </c>
       <c r="I243" t="n">
-        <v>1.0363</v>
+        <v>0.9906</v>
       </c>
       <c r="J243" t="n">
-        <v>22.7986</v>
+        <v>21.7932</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>1.18</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4818</v>
+        <v>0.4808</v>
       </c>
       <c r="J244" t="n">
-        <v>10.5996</v>
+        <v>10.5776</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>1.09</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2399</v>
+        <v>0.26</v>
       </c>
       <c r="J245" t="n">
-        <v>5.2778</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.96</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2514</v>
+        <v>-0.2295</v>
       </c>
       <c r="J246" t="n">
-        <v>-5.5308</v>
+        <v>-5.049</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>0.86</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1358</v>
+        <v>-0.1587</v>
       </c>
       <c r="J247" t="n">
-        <v>-2.9876</v>
+        <v>-3.4914</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>0.82</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1798</v>
+        <v>-0.2023</v>
       </c>
       <c r="J248" t="n">
-        <v>-3.9556</v>
+        <v>-4.4506</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.75</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2515</v>
+        <v>-0.2725</v>
       </c>
       <c r="J249" t="n">
-        <v>-5.533</v>
+        <v>-5.995</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.61</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3805</v>
+        <v>-0.3974</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.371</v>
+        <v>-8.742800000000001</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.48</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5021</v>
+        <v>-0.512</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.0462</v>
+        <v>-11.264</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.6</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2502</v>
+        <v>1.2237</v>
       </c>
       <c r="J252" t="n">
-        <v>28.7546</v>
+        <v>28.1451</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.45</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0626</v>
+        <v>1.0187</v>
       </c>
       <c r="J253" t="n">
-        <v>24.4398</v>
+        <v>23.4301</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>1.2</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.5369</v>
       </c>
       <c r="J254" t="n">
-        <v>12.6017</v>
+        <v>12.3487</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>1.18</v>
       </c>
       <c r="I255" t="n">
-        <v>0.4984</v>
+        <v>0.4924</v>
       </c>
       <c r="J255" t="n">
-        <v>11.4632</v>
+        <v>11.3252</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.92</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3614</v>
+        <v>-0.3374</v>
       </c>
       <c r="J256" t="n">
-        <v>-8.312200000000001</v>
+        <v>-7.7602</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.21</v>
       </c>
       <c r="I257" t="n">
-        <v>0.574</v>
+        <v>0.5371</v>
       </c>
       <c r="J257" t="n">
-        <v>13.202</v>
+        <v>12.3533</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>0.8</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2117</v>
+        <v>-0.2313</v>
       </c>
       <c r="J258" t="n">
-        <v>-4.8691</v>
+        <v>-5.3199</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>0.67</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3337</v>
+        <v>-0.3509</v>
       </c>
       <c r="J259" t="n">
-        <v>-7.6751</v>
+        <v>-8.0707</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.67</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3337</v>
+        <v>-0.3509</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.6751</v>
+        <v>-8.0707</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.47</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5202</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.9646</v>
+        <v>-12.1371</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.14</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3292</v>
+        <v>0.3305</v>
       </c>
       <c r="J262" t="n">
-        <v>9.875999999999999</v>
+        <v>9.914999999999999</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.07</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1864</v>
+        <v>0.1936</v>
       </c>
       <c r="J263" t="n">
-        <v>5.592</v>
+        <v>5.808</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.02</v>
       </c>
       <c r="I264" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J264" t="n">
-        <v>2.043</v>
+        <v>2.244</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.97</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.049</v>
+        <v>-0.0574</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.47</v>
+        <v>-1.722</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.74</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2966</v>
+        <v>-0.3093</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.898</v>
+        <v>-9.279</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.21</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6339</v>
+        <v>0.6012</v>
       </c>
       <c r="J267" t="n">
-        <v>19.017</v>
+        <v>18.036</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5824</v>
+        <v>0.5554</v>
       </c>
       <c r="J268" t="n">
-        <v>17.472</v>
+        <v>16.662</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.98</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1005</v>
+        <v>-0.1042</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.015</v>
+        <v>-3.126</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.97</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1374</v>
+        <v>-0.1405</v>
       </c>
       <c r="J270" t="n">
-        <v>-4.122</v>
+        <v>-4.215</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.8</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6301</v>
+        <v>-0.5937</v>
       </c>
       <c r="J271" t="n">
-        <v>-18.903</v>
+        <v>-17.811</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6477/event_6477_evp_summary.xlsx
+++ b/database/event/6477/event_6477_evp_summary.xlsx
@@ -492,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.5897</v>
+        <v>4.58</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5028</v>
+        <v>0.5017</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4651</v>
+        <v>1.4806</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5897</v>
+        <v>4.58</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3178</v>
+        <v>3.8287</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2719</v>
+        <v>0.7513</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7254</v>
+        <v>5.8241</v>
       </c>
       <c r="I2" t="n">
-        <v>6.7254</v>
+        <v>6.3035</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2719</v>
+        <v>0.7513</v>
       </c>
       <c r="K2" t="n">
-        <v>155</v>
+        <v>262</v>
       </c>
       <c r="L2" t="n">
         <v>52</v>
       </c>
       <c r="M2" t="n">
-        <v>6.997299999999999</v>
+        <v>7.054799999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>207</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.5701</v>
+        <v>4.5205</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5006</v>
+        <v>0.4952</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4562</v>
+        <v>1.4535</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5701</v>
+        <v>4.5205</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8784</v>
+        <v>4.2873</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6917</v>
+        <v>0.2332</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7637</v>
+        <v>6.8751</v>
       </c>
       <c r="I3" t="n">
-        <v>6.2209</v>
+        <v>6.8751</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6917</v>
+        <v>0.2332</v>
       </c>
       <c r="K3" t="n">
-        <v>262</v>
+        <v>155</v>
       </c>
       <c r="L3" t="n">
         <v>52</v>
       </c>
       <c r="M3" t="n">
-        <v>6.9126</v>
+        <v>7.1083</v>
       </c>
       <c r="N3" t="n">
-        <v>314</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4">
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.288</v>
+        <v>4.2717</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4697</v>
+        <v>0.4679</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3278</v>
+        <v>1.3402</v>
       </c>
       <c r="E4" t="n">
-        <v>4.288</v>
+        <v>4.2717</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4325</v>
+        <v>2.4447</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8555</v>
+        <v>1.827</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5991</v>
+        <v>2.6523</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8052</v>
+        <v>2.8707</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8555</v>
+        <v>1.827</v>
       </c>
       <c r="K4" t="n">
         <v>262</v>
@@ -621,7 +621,7 @@
         <v>52</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6607</v>
+        <v>4.697699999999999</v>
       </c>
       <c r="N4" t="n">
         <v>314</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2779</v>
+        <v>3.3881</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3591</v>
+        <v>0.3712</v>
       </c>
       <c r="D5" t="n">
-        <v>0.868</v>
+        <v>0.9377</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2779</v>
+        <v>3.3881</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9535</v>
+        <v>2.101</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3244</v>
+        <v>1.2871</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9535</v>
+        <v>2.101</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1084</v>
+        <v>2.274</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3244</v>
+        <v>1.2871</v>
       </c>
       <c r="K5" t="n">
         <v>262</v>
@@ -667,7 +667,7 @@
         <v>52</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4328</v>
+        <v>3.5611</v>
       </c>
       <c r="N5" t="n">
         <v>314</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.249</v>
+        <v>3.1492</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3559</v>
+        <v>0.345</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8548</v>
+        <v>0.8288</v>
       </c>
       <c r="E6" t="n">
-        <v>3.249</v>
+        <v>3.1492</v>
       </c>
       <c r="F6" t="n">
-        <v>3.249</v>
+        <v>3.1492</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3861</v>
+        <v>4.2669</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3861</v>
+        <v>4.2669</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3861</v>
+        <v>4.2669</v>
       </c>
       <c r="N6" t="n">
         <v>194</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4455</v>
+        <v>2.4371</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2679</v>
+        <v>0.267</v>
       </c>
       <c r="D7" t="n">
-        <v>0.489</v>
+        <v>0.5044</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4455</v>
+        <v>2.4371</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4455</v>
+        <v>2.4371</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6276</v>
+        <v>2.635</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6276</v>
+        <v>2.635</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6276</v>
+        <v>2.635</v>
       </c>
       <c r="N7" t="n">
         <v>194</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4453</v>
+        <v>2.355</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2679</v>
+        <v>0.258</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4889</v>
+        <v>0.467</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4453</v>
+        <v>2.355</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4453</v>
+        <v>2.6456</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0.2906</v>
       </c>
       <c r="H8" t="n">
-        <v>2.627</v>
+        <v>3.1127</v>
       </c>
       <c r="I8" t="n">
-        <v>2.627</v>
+        <v>3.3689</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.2906</v>
       </c>
       <c r="K8" t="n">
-        <v>211</v>
+        <v>262</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M8" t="n">
-        <v>2.627</v>
+        <v>3.0783</v>
       </c>
       <c r="N8" t="n">
-        <v>211</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3991</v>
+        <v>2.3521</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2628</v>
+        <v>0.2577</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4679</v>
+        <v>0.4657</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3991</v>
+        <v>2.3521</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3991</v>
+        <v>2.3521</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.526</v>
+        <v>2.4403</v>
       </c>
       <c r="I9" t="n">
-        <v>2.526</v>
+        <v>2.4403</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.526</v>
+        <v>2.4403</v>
       </c>
       <c r="N9" t="n">
-        <v>159</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3766</v>
+        <v>2.2712</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2603</v>
+        <v>0.2488</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4577</v>
+        <v>0.4289</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3766</v>
+        <v>2.2712</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7267</v>
+        <v>2.2712</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3501</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.243</v>
+        <v>2.2712</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5002</v>
+        <v>2.2712</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3501</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>262</v>
+        <v>159</v>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1501</v>
+        <v>2.2712</v>
       </c>
       <c r="N10" t="n">
-        <v>314</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1896</v>
+        <v>1.9801</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2399</v>
+        <v>0.2169</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3725</v>
+        <v>0.2962</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1896</v>
+        <v>1.9801</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1896</v>
+        <v>1.9801</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1896</v>
+        <v>1.9801</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1896</v>
+        <v>1.9801</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1896</v>
+        <v>1.9801</v>
       </c>
       <c r="N11" t="n">
         <v>194</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.956</v>
+        <v>1.7912</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2143</v>
+        <v>0.1962</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2662</v>
+        <v>0.2102</v>
       </c>
       <c r="E12" t="n">
-        <v>1.956</v>
+        <v>1.7912</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7439</v>
+        <v>1.6255</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2121</v>
+        <v>0.1657</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7439</v>
+        <v>1.6255</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7439</v>
+        <v>1.6255</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2121</v>
+        <v>0.1657</v>
       </c>
       <c r="K12" t="n">
         <v>155</v>
@@ -989,7 +989,7 @@
         <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>1.956</v>
+        <v>1.7912</v>
       </c>
       <c r="N12" t="n">
         <v>207</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7575</v>
+        <v>1.7401</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1925</v>
+        <v>0.1906</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1758</v>
+        <v>0.1869</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7575</v>
+        <v>1.7401</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7575</v>
+        <v>1.7401</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7575</v>
+        <v>1.7401</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7575</v>
+        <v>1.7401</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7575</v>
+        <v>1.7401</v>
       </c>
       <c r="N13" t="n">
         <v>69</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4377</v>
+        <v>1.5458</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1575</v>
+        <v>0.1693</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0303</v>
+        <v>0.0984</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4377</v>
+        <v>1.5458</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2857</v>
+        <v>1.3911</v>
       </c>
       <c r="G14" t="n">
-        <v>0.152</v>
+        <v>0.1547</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2857</v>
+        <v>1.3911</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3877</v>
+        <v>1.5056</v>
       </c>
       <c r="J14" t="n">
-        <v>0.152</v>
+        <v>0.1547</v>
       </c>
       <c r="K14" t="n">
         <v>262</v>
@@ -1081,7 +1081,7 @@
         <v>52</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5397</v>
+        <v>1.6603</v>
       </c>
       <c r="N14" t="n">
         <v>314</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4177</v>
+        <v>1.2375</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1553</v>
+        <v>0.1356</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0212</v>
+        <v>-0.042</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4177</v>
+        <v>1.2375</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4177</v>
+        <v>1.2375</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4177</v>
+        <v>1.2375</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4177</v>
+        <v>1.2375</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4177</v>
+        <v>1.2375</v>
       </c>
       <c r="N15" t="n">
         <v>165</v>
@@ -1136,139 +1136,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2319</v>
+        <v>1.1457</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1349</v>
+        <v>0.1255</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0634</v>
+        <v>-0.0839</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2319</v>
+        <v>1.1457</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2319</v>
+        <v>1.1457</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2319</v>
+        <v>1.1457</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2319</v>
+        <v>1.1457</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2319</v>
+        <v>1.1457</v>
       </c>
       <c r="N16" t="n">
-        <v>159</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1539</v>
+        <v>1.037</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1264</v>
+        <v>0.1136</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0989</v>
+        <v>-0.1334</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1539</v>
+        <v>1.037</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1539</v>
+        <v>1.037</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1539</v>
+        <v>1.037</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1539</v>
+        <v>1.037</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1539</v>
+        <v>1.037</v>
       </c>
       <c r="N17" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0681</v>
+        <v>0.9784</v>
       </c>
       <c r="C18" t="n">
-        <v>0.117</v>
+        <v>0.1072</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.138</v>
+        <v>-0.1601</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0681</v>
+        <v>0.9784</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0681</v>
+        <v>0.9784</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0681</v>
+        <v>0.9784</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0681</v>
+        <v>0.9784</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0681</v>
+        <v>0.9784</v>
       </c>
       <c r="N18" t="n">
-        <v>211</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0543</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1155</v>
+        <v>0.1036</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1443</v>
+        <v>-0.1748</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0543</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0543</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0543</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0543</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0543</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="N19" t="n">
         <v>165</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8824</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.1016</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2225</v>
+        <v>-0.1831</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8824</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8824</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8824</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8824</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8824</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>99</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6763</v>
+        <v>0.632</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0741</v>
+        <v>0.0692</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3163</v>
+        <v>-0.3179</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6763</v>
+        <v>0.632</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6763</v>
+        <v>0.632</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6763</v>
+        <v>0.632</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6763</v>
+        <v>0.632</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6763</v>
+        <v>0.632</v>
       </c>
       <c r="N21" t="n">
-        <v>159</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.501</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0712</v>
+        <v>0.0549</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3284</v>
+        <v>-0.3776</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.501</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.501</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.501</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.501</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>211</v>
+        <v>159</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.501</v>
       </c>
       <c r="N22" t="n">
-        <v>211</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.373</v>
+        <v>0.402</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0409</v>
+        <v>0.044</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4544</v>
+        <v>-0.4227</v>
       </c>
       <c r="E23" t="n">
-        <v>0.373</v>
+        <v>0.402</v>
       </c>
       <c r="F23" t="n">
-        <v>0.373</v>
+        <v>0.402</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.373</v>
+        <v>0.402</v>
       </c>
       <c r="I23" t="n">
-        <v>0.373</v>
+        <v>0.402</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.373</v>
+        <v>0.402</v>
       </c>
       <c r="N23" t="n">
         <v>71</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3312</v>
+        <v>0.2949</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0363</v>
+        <v>0.0323</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4734</v>
+        <v>-0.4714</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3312</v>
+        <v>0.2949</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0743</v>
+        <v>1.0147</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7431</v>
+        <v>-0.7198</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0743</v>
+        <v>1.0147</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0743</v>
+        <v>1.0147</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7431</v>
+        <v>-0.7198</v>
       </c>
       <c r="K24" t="n">
         <v>155</v>
@@ -1541,7 +1541,7 @@
         <v>52</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3312</v>
+        <v>0.2948999999999999</v>
       </c>
       <c r="N24" t="n">
         <v>207</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1783</v>
+        <v>0.1694</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0195</v>
+        <v>0.0186</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.543</v>
+        <v>-0.5286</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1783</v>
+        <v>0.1694</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1783</v>
+        <v>0.1694</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1783</v>
+        <v>0.1694</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1783</v>
+        <v>0.1694</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1783</v>
+        <v>0.1694</v>
       </c>
       <c r="N25" t="n">
         <v>159</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1634</v>
+        <v>0.0144</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0179</v>
+        <v>0.0016</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5498</v>
+        <v>-0.5992</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1634</v>
+        <v>0.0144</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1634</v>
+        <v>0.0144</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1634</v>
+        <v>0.0144</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1634</v>
+        <v>0.0144</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1634</v>
+        <v>0.0144</v>
       </c>
       <c r="N26" t="n">
         <v>194</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0438</v>
+        <v>-0.0848</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0048</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6441</v>
+        <v>-0.6444</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0438</v>
+        <v>-0.0848</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.9454</v>
+        <v>-0.886</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9016</v>
+        <v>0.8012</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.9454</v>
+        <v>-0.886</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9454</v>
+        <v>-0.886</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9016</v>
+        <v>0.8012</v>
       </c>
       <c r="K27" t="n">
         <v>155</v>
@@ -1679,7 +1679,7 @@
         <v>52</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.04380000000000006</v>
+        <v>-0.08479999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>207</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1812</v>
+        <v>-0.1537</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0198</v>
+        <v>-0.0168</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7067</v>
+        <v>-0.6758</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1812</v>
+        <v>-0.1537</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4362</v>
+        <v>0.4288</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.5825</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4362</v>
+        <v>0.4288</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4362</v>
+        <v>0.4288</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.5825</v>
       </c>
       <c r="K28" t="n">
         <v>155</v>
@@ -1725,7 +1725,7 @@
         <v>52</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1812</v>
+        <v>-0.1537</v>
       </c>
       <c r="N28" t="n">
         <v>207</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2898</v>
+        <v>-0.2796</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0317</v>
+        <v>-0.0306</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7561</v>
+        <v>-0.7332</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2898</v>
+        <v>-0.2796</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2898</v>
+        <v>-0.2796</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2898</v>
+        <v>-0.2796</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2898</v>
+        <v>-0.2796</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2898</v>
+        <v>-0.2796</v>
       </c>
       <c r="N29" t="n">
         <v>194</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3852</v>
+        <v>-0.4019</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0422</v>
+        <v>-0.044</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7996</v>
+        <v>-0.7889</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3852</v>
+        <v>-0.4019</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3852</v>
+        <v>-0.4019</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3852</v>
+        <v>-0.4019</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3852</v>
+        <v>-0.4019</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3852</v>
+        <v>-0.4019</v>
       </c>
       <c r="N30" t="n">
         <v>112</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4009</v>
+        <v>-0.4297</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0439</v>
+        <v>-0.0471</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8067</v>
+        <v>-0.8015</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4009</v>
+        <v>-0.4297</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4009</v>
+        <v>-0.4297</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4009</v>
+        <v>-0.4297</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4009</v>
+        <v>-0.4297</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4009</v>
+        <v>-0.4297</v>
       </c>
       <c r="N31" t="n">
         <v>71</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6199</v>
+        <v>-0.5705</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0679</v>
+        <v>-0.0625</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9064</v>
+        <v>-0.8657</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6199</v>
+        <v>-0.5705</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6199</v>
+        <v>-0.5705</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6199</v>
+        <v>-0.5705</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6199</v>
+        <v>-0.5705</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6199</v>
+        <v>-0.5705</v>
       </c>
       <c r="N32" t="n">
         <v>71</v>
@@ -1918,139 +1918,139 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7066</v>
+        <v>-0.645</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0774</v>
+        <v>-0.0707</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9459</v>
+        <v>-0.8996</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7066</v>
+        <v>-0.645</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7066</v>
+        <v>-0.645</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7066</v>
+        <v>-0.645</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7066</v>
+        <v>-0.645</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7066</v>
+        <v>-0.645</v>
       </c>
       <c r="N33" t="n">
-        <v>165</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>djay</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7086</v>
+        <v>-0.7252</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0776</v>
+        <v>-0.0794</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9468</v>
+        <v>-0.9362</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7086</v>
+        <v>-0.7252</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7086</v>
+        <v>-0.7252</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7086</v>
+        <v>-0.7252</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7086</v>
+        <v>-0.7252</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7086</v>
+        <v>-0.7252</v>
       </c>
       <c r="N34" t="n">
-        <v>211</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>djay</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7605</v>
+        <v>-0.7611</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0833</v>
+        <v>-0.0834</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9704</v>
+        <v>-0.9525</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7605</v>
+        <v>-0.7611</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7605</v>
+        <v>-0.7611</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7605</v>
+        <v>-0.7611</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7605</v>
+        <v>-0.7611</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7605</v>
+        <v>-0.7611</v>
       </c>
       <c r="N35" t="n">
-        <v>71</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.853</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.0934</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0255</v>
+        <v>-0.9944</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.853</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.853</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.853</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.853</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.853</v>
       </c>
       <c r="N36" t="n">
         <v>69</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9366</v>
+        <v>-0.9217</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1026</v>
+        <v>-0.101</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0506</v>
+        <v>-1.0257</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9366</v>
+        <v>-0.9217</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9366</v>
+        <v>-0.9217</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9366</v>
+        <v>-0.9217</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9366</v>
+        <v>-0.9217</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9366</v>
+        <v>-0.9217</v>
       </c>
       <c r="N37" t="n">
         <v>165</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9694</v>
+        <v>-0.9398</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1062</v>
+        <v>-0.103</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0655</v>
+        <v>-1.0339</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9694</v>
+        <v>-0.9398</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9694</v>
+        <v>-0.9398</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9694</v>
+        <v>-0.9398</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9694</v>
+        <v>-0.9398</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9694</v>
+        <v>-0.9398</v>
       </c>
       <c r="N38" t="n">
         <v>69</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1117</v>
+        <v>-1.0828</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1218</v>
+        <v>-0.1186</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1303</v>
+        <v>-1.0991</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1117</v>
+        <v>-1.0828</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1117</v>
+        <v>-1.0828</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1117</v>
+        <v>-1.0828</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1117</v>
+        <v>-1.0828</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1117</v>
+        <v>-1.0828</v>
       </c>
       <c r="N39" t="n">
         <v>69</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1812</v>
+        <v>-1.1584</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1294</v>
+        <v>-0.1269</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1619</v>
+        <v>-1.1335</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1812</v>
+        <v>-1.1584</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.1812</v>
+        <v>-1.1584</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.1812</v>
+        <v>-1.1584</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1812</v>
+        <v>-1.1584</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1812</v>
+        <v>-1.1584</v>
       </c>
       <c r="N40" t="n">
         <v>69</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4636</v>
+        <v>-1.4561</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1603</v>
+        <v>-0.1595</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2905</v>
+        <v>-1.2691</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4636</v>
+        <v>-1.4561</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4636</v>
+        <v>-1.4561</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4636</v>
+        <v>-1.4561</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4636</v>
+        <v>-1.4561</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4636</v>
+        <v>-1.4561</v>
       </c>
       <c r="N41" t="n">
         <v>71</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-1.6295</v>
+        <v>-1.5943</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.1785</v>
+        <v>-0.1746</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.366</v>
+        <v>-1.3321</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.6295</v>
+        <v>-1.5943</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.6295</v>
+        <v>-1.5943</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.6295</v>
+        <v>-1.5943</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.6295</v>
+        <v>-1.5943</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-1.6295</v>
+        <v>-1.5943</v>
       </c>
       <c r="N42" t="n">
         <v>159</v>
@@ -2475,10 +2475,10 @@
         <v>1.35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6983</v>
+        <v>0.6454</v>
       </c>
       <c r="J2" t="n">
-        <v>17.4575</v>
+        <v>16.135</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0055</v>
       </c>
       <c r="J3" t="n">
-        <v>0.22</v>
+        <v>0.1375</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1953</v>
+        <v>-0.1752</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.8825</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.76</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.285</v>
+        <v>-0.2662</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.125</v>
+        <v>-6.655</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3414</v>
+        <v>-0.3257</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.535</v>
+        <v>-8.1425</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0357</v>
+        <v>1.0312</v>
       </c>
       <c r="J7" t="n">
-        <v>25.8925</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.44</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0357</v>
+        <v>1.0312</v>
       </c>
       <c r="J8" t="n">
-        <v>25.8925</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4144</v>
+        <v>0.3785</v>
       </c>
       <c r="J9" t="n">
-        <v>10.36</v>
+        <v>9.4625</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>0.99</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0877</v>
+        <v>-0.0668</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1925</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>0.83</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5498</v>
+        <v>-0.5113</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.745</v>
+        <v>-12.7825</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.21</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4672</v>
+        <v>0.41</v>
       </c>
       <c r="J12" t="n">
-        <v>12.6144</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>1.07</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2033</v>
+        <v>0.1614</v>
       </c>
       <c r="J13" t="n">
-        <v>5.4891</v>
+        <v>4.3578</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>1.07</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2033</v>
+        <v>0.1614</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4891</v>
+        <v>4.3578</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.77</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.276</v>
+        <v>-0.2568</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.452</v>
+        <v>-6.9336</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.57</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4581</v>
+        <v>-0.4536</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.3687</v>
+        <v>-12.2472</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.55</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2415</v>
+        <v>1.2626</v>
       </c>
       <c r="J17" t="n">
-        <v>33.5205</v>
+        <v>34.0902</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.33</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8198</v>
+        <v>0.7958</v>
       </c>
       <c r="J18" t="n">
-        <v>22.1346</v>
+        <v>21.4866</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2887</v>
+        <v>0.2559</v>
       </c>
       <c r="J19" t="n">
-        <v>7.7949</v>
+        <v>6.9093</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2624</v>
+        <v>-0.2238</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.0848</v>
+        <v>-6.0426</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2624</v>
+        <v>-0.2238</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.0848</v>
+        <v>-6.0426</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9674</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>32.8916</v>
+        <v>32.6128</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.23</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6353</v>
+        <v>0.5984</v>
       </c>
       <c r="J23" t="n">
-        <v>21.6002</v>
+        <v>20.3456</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1109</v>
+        <v>-0.0849</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.7706</v>
+        <v>-2.8866</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>0.92</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.301</v>
+        <v>-0.2597</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.234</v>
+        <v>-8.829800000000001</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.82</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5547</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-18.8598</v>
+        <v>-17.4964</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.08</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2171</v>
+        <v>0.1738</v>
       </c>
       <c r="J27" t="n">
-        <v>7.3814</v>
+        <v>5.9092</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.152</v>
+        <v>0.1168</v>
       </c>
       <c r="J28" t="n">
-        <v>5.168</v>
+        <v>3.9712</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>0.93</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1095</v>
+        <v>-0.0922</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.723</v>
+        <v>-3.1348</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1332</v>
+        <v>-0.1145</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.5288</v>
+        <v>-3.893</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.9</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1447</v>
+        <v>-0.1254</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.9198</v>
+        <v>-4.2636</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7736</v>
+        <v>0.7452</v>
       </c>
       <c r="J32" t="n">
-        <v>20.1136</v>
+        <v>19.3752</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4909</v>
+        <v>0.4515</v>
       </c>
       <c r="J33" t="n">
-        <v>12.7634</v>
+        <v>11.739</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.14</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4207</v>
+        <v>0.3817</v>
       </c>
       <c r="J34" t="n">
-        <v>10.9382</v>
+        <v>9.924200000000001</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>0.99</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0772</v>
+        <v>-0.0568</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.0072</v>
+        <v>-1.4768</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.95</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2208</v>
+        <v>-0.1838</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.7408</v>
+        <v>-4.7788</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4376</v>
+        <v>0.38</v>
       </c>
       <c r="J37" t="n">
-        <v>11.3776</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2555</v>
+        <v>0.2085</v>
       </c>
       <c r="J38" t="n">
-        <v>6.643</v>
+        <v>5.421</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1727</v>
+        <v>0.1349</v>
       </c>
       <c r="J39" t="n">
-        <v>4.4902</v>
+        <v>3.5074</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2309</v>
+        <v>-0.2105</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.0034</v>
+        <v>-5.473</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.309</v>
+        <v>-0.2915</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.034000000000001</v>
+        <v>-7.579</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>0.76</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.2562</v>
+        <v>-0.2424</v>
       </c>
       <c r="J42" t="n">
-        <v>-5.8926</v>
+        <v>-5.5752</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>0.73</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2855</v>
+        <v>-0.2726</v>
       </c>
       <c r="J43" t="n">
-        <v>-6.5665</v>
+        <v>-6.2698</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>0.68</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3318</v>
+        <v>-0.3198</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.6314</v>
+        <v>-7.3554</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>0.62</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3834</v>
+        <v>-0.3725</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.818199999999999</v>
+        <v>-8.567500000000001</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>0.52</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4714</v>
+        <v>-0.4665</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.8422</v>
+        <v>-10.7295</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2851</v>
+        <v>1.3038</v>
       </c>
       <c r="J47" t="n">
-        <v>29.5573</v>
+        <v>29.9874</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>1.49</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0639</v>
+        <v>1.074</v>
       </c>
       <c r="J48" t="n">
-        <v>24.4697</v>
+        <v>24.702</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>1.33</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7743</v>
       </c>
       <c r="J49" t="n">
-        <v>18.2114</v>
+        <v>17.8089</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>1.2</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5248</v>
+        <v>0.4957</v>
       </c>
       <c r="J50" t="n">
-        <v>12.0704</v>
+        <v>11.4011</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>1.08</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2318</v>
+        <v>0.2013</v>
       </c>
       <c r="J51" t="n">
-        <v>5.3314</v>
+        <v>4.6299</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.16</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3676</v>
+        <v>0.3128</v>
       </c>
       <c r="J52" t="n">
-        <v>10.6604</v>
+        <v>9.071199999999999</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3314</v>
+        <v>0.2786</v>
       </c>
       <c r="J53" t="n">
-        <v>9.6106</v>
+        <v>8.0794</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>0.99</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0246</v>
+        <v>-0.0179</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.7134</v>
+        <v>-0.5191</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.91</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1341</v>
+        <v>-0.1152</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.8889</v>
+        <v>-3.3408</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.72</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3277</v>
+        <v>-0.3114</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.503299999999999</v>
+        <v>-9.0306</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.4</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9707</v>
+        <v>0.9624</v>
       </c>
       <c r="J57" t="n">
-        <v>28.1503</v>
+        <v>27.9096</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.15</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4434</v>
+        <v>0.4045</v>
       </c>
       <c r="J58" t="n">
-        <v>12.8586</v>
+        <v>11.7305</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>1.12</v>
       </c>
       <c r="I59" t="n">
-        <v>0.372</v>
+        <v>0.3343</v>
       </c>
       <c r="J59" t="n">
-        <v>10.788</v>
+        <v>9.694699999999999</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>1.07</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2424</v>
+        <v>0.2102</v>
       </c>
       <c r="J60" t="n">
-        <v>7.0296</v>
+        <v>6.0958</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5163</v>
+        <v>-0.4756</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.9727</v>
+        <v>-13.7924</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.68</v>
       </c>
       <c r="I62" t="n">
-        <v>1.3222</v>
+        <v>1.3427</v>
       </c>
       <c r="J62" t="n">
-        <v>31.7328</v>
+        <v>32.2248</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.48</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0588</v>
+        <v>1.0668</v>
       </c>
       <c r="J63" t="n">
-        <v>25.4112</v>
+        <v>25.6032</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>1.26</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6604</v>
+        <v>0.634</v>
       </c>
       <c r="J64" t="n">
-        <v>15.8496</v>
+        <v>15.216</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>1.06</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1839</v>
+        <v>0.1561</v>
       </c>
       <c r="J65" t="n">
-        <v>4.4136</v>
+        <v>3.7464</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.99</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1094</v>
+        <v>-0.0895</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.6256</v>
+        <v>-2.148</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.16</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4285</v>
+        <v>0.3807</v>
       </c>
       <c r="J67" t="n">
-        <v>10.284</v>
+        <v>9.136799999999999</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.12</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3505</v>
+        <v>0.3042</v>
       </c>
       <c r="J68" t="n">
-        <v>8.412000000000001</v>
+        <v>7.3008</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1516</v>
+        <v>-0.1359</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.6384</v>
+        <v>-3.2616</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.45</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5482</v>
+        <v>-0.554</v>
       </c>
       <c r="J70" t="n">
-        <v>-13.1568</v>
+        <v>-13.296</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.37</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6161</v>
+        <v>-0.6332</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.7864</v>
+        <v>-15.1968</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>0.92</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.1092</v>
+        <v>-0.0948</v>
       </c>
       <c r="J72" t="n">
-        <v>-2.5116</v>
+        <v>-2.1804</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>0.91</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1213</v>
+        <v>-0.1063</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.7899</v>
+        <v>-2.4449</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>0.87</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1664</v>
+        <v>-0.1496</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.8272</v>
+        <v>-3.4408</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>0.72</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3121</v>
+        <v>-0.295</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.1783</v>
+        <v>-6.785</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3121</v>
+        <v>-0.295</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.1783</v>
+        <v>-6.785</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.79</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8985</v>
+        <v>0.8306</v>
       </c>
       <c r="J77" t="n">
-        <v>20.6655</v>
+        <v>19.1038</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.54</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6577</v>
+        <v>0.5857</v>
       </c>
       <c r="J78" t="n">
-        <v>15.1271</v>
+        <v>13.4711</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>1.16</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2466</v>
+        <v>0.2011</v>
       </c>
       <c r="J79" t="n">
-        <v>5.6718</v>
+        <v>4.6253</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.89</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1783</v>
+        <v>-0.1592</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.1009</v>
+        <v>-3.6616</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.87</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2003</v>
+        <v>-0.1812</v>
       </c>
       <c r="J81" t="n">
-        <v>-4.6069</v>
+        <v>-4.1676</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.93</v>
       </c>
       <c r="I82" t="n">
-        <v>1.5863</v>
+        <v>1.6243</v>
       </c>
       <c r="J82" t="n">
-        <v>31.726</v>
+        <v>32.486</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.93</v>
       </c>
       <c r="I83" t="n">
-        <v>1.5863</v>
+        <v>1.6243</v>
       </c>
       <c r="J83" t="n">
-        <v>31.726</v>
+        <v>32.486</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1.64</v>
       </c>
       <c r="I84" t="n">
-        <v>1.2376</v>
+        <v>1.2574</v>
       </c>
       <c r="J84" t="n">
-        <v>24.752</v>
+        <v>25.148</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>1.03</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0571</v>
+        <v>0.032</v>
       </c>
       <c r="J85" t="n">
-        <v>1.142</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.98</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1815</v>
+        <v>-0.161</v>
       </c>
       <c r="J86" t="n">
-        <v>-3.63</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>0.77</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.2299</v>
+        <v>-0.2144</v>
       </c>
       <c r="J87" t="n">
-        <v>-4.598</v>
+        <v>-4.288</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>0.7</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.3014</v>
+        <v>-0.2902</v>
       </c>
       <c r="J88" t="n">
-        <v>-6.028</v>
+        <v>-5.804</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>0.61</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3848</v>
+        <v>-0.377</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.696</v>
+        <v>-7.54</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.54</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4439</v>
+        <v>-0.438</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.878</v>
+        <v>-8.76</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.34</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6202</v>
+        <v>-0.6348</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.404</v>
+        <v>-12.696</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.41</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9771</v>
+        <v>0.9697</v>
       </c>
       <c r="J92" t="n">
-        <v>24.4275</v>
+        <v>24.2425</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.33</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8227</v>
+        <v>0.7986</v>
       </c>
       <c r="J93" t="n">
-        <v>20.5675</v>
+        <v>19.965</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2636</v>
+        <v>0.2315</v>
       </c>
       <c r="J94" t="n">
-        <v>6.59</v>
+        <v>5.7875</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>1.04</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1451</v>
+        <v>0.1208</v>
       </c>
       <c r="J95" t="n">
-        <v>3.6275</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.93</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2896</v>
+        <v>-0.2496</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.24</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.32</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.5816</v>
       </c>
       <c r="J97" t="n">
-        <v>15.965</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>1.14</v>
       </c>
       <c r="I98" t="n">
-        <v>0.335</v>
+        <v>0.282</v>
       </c>
       <c r="J98" t="n">
-        <v>8.375</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>1.13</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3164</v>
+        <v>0.2645</v>
       </c>
       <c r="J99" t="n">
-        <v>7.91</v>
+        <v>6.6125</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>0.65</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3902</v>
+        <v>-0.3787</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.755000000000001</v>
+        <v>-9.467499999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.6</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4345</v>
+        <v>-0.4276</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.8625</v>
+        <v>-10.69</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.57</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2048</v>
+        <v>1.2204</v>
       </c>
       <c r="J102" t="n">
-        <v>30.12</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.15</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4366</v>
+        <v>0.4009</v>
       </c>
       <c r="J103" t="n">
-        <v>10.915</v>
+        <v>10.0225</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>1.13</v>
       </c>
       <c r="I104" t="n">
-        <v>0.389</v>
+        <v>0.3539</v>
       </c>
       <c r="J104" t="n">
-        <v>9.725</v>
+        <v>8.8475</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>1.1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3138</v>
+        <v>0.2803</v>
       </c>
       <c r="J105" t="n">
-        <v>7.845</v>
+        <v>7.0075</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2639</v>
+        <v>-0.2253</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.5975</v>
+        <v>-5.6325</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.14</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3719</v>
+        <v>0.3212</v>
       </c>
       <c r="J107" t="n">
-        <v>9.297499999999999</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>0.84</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1983</v>
+        <v>-0.1802</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.9575</v>
+        <v>-4.505</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>0.82</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2179</v>
+        <v>-0.1994</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.4475</v>
+        <v>-4.985</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2277</v>
+        <v>-0.2091</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.6925</v>
+        <v>-5.2275</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.6</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4225</v>
+        <v>-0.4131</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.5625</v>
+        <v>-10.3275</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.55</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1777</v>
+        <v>1.1921</v>
       </c>
       <c r="J112" t="n">
-        <v>35.331</v>
+        <v>35.763</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.37</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8973</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="J113" t="n">
-        <v>26.919</v>
+        <v>26.385</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.36</v>
       </c>
       <c r="I114" t="n">
-        <v>0.8776</v>
+        <v>0.8582</v>
       </c>
       <c r="J114" t="n">
-        <v>26.328</v>
+        <v>25.746</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>0.85</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5034</v>
+        <v>-0.4635</v>
       </c>
       <c r="J115" t="n">
-        <v>-15.102</v>
+        <v>-13.905</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.76</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7118</v>
+        <v>-0.6832</v>
       </c>
       <c r="J116" t="n">
-        <v>-21.354</v>
+        <v>-20.496</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.15</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3692</v>
+        <v>0.3154</v>
       </c>
       <c r="J117" t="n">
-        <v>11.076</v>
+        <v>9.462</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.09</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2525</v>
+        <v>0.206</v>
       </c>
       <c r="J118" t="n">
-        <v>7.575</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.91</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1287</v>
+        <v>-0.1116</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.861</v>
+        <v>-3.348</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.9</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1397</v>
+        <v>-0.122</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.191</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.49</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5243</v>
+        <v>-0.5281</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.729</v>
+        <v>-15.843</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.32</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.7982</v>
       </c>
       <c r="J122" t="n">
-        <v>23.8699</v>
+        <v>23.1478</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.24</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6535</v>
+        <v>0.6177</v>
       </c>
       <c r="J123" t="n">
-        <v>18.9515</v>
+        <v>17.9133</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>1.05</v>
       </c>
       <c r="I124" t="n">
-        <v>0.189</v>
+        <v>0.1594</v>
       </c>
       <c r="J124" t="n">
-        <v>5.481</v>
+        <v>4.6226</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>0.9</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3582</v>
+        <v>-0.3156</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.3878</v>
+        <v>-9.1524</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.9</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3582</v>
+        <v>-0.3156</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.3878</v>
+        <v>-9.1524</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.24</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5253</v>
+        <v>0.4687</v>
       </c>
       <c r="J127" t="n">
-        <v>15.2337</v>
+        <v>13.5923</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>0.91</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.129</v>
+        <v>-0.1117</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.741</v>
+        <v>-3.2393</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>0.89</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1512</v>
+        <v>-0.1327</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.3848</v>
+        <v>-3.8483</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.86</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1834</v>
+        <v>-0.1638</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.3186</v>
+        <v>-4.7502</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3582</v>
+        <v>-0.3436</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.3878</v>
+        <v>-9.964399999999999</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.56</v>
       </c>
       <c r="I132" t="n">
-        <v>1.2236</v>
+        <v>1.244</v>
       </c>
       <c r="J132" t="n">
-        <v>36.708</v>
+        <v>37.32</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>1.04</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1602</v>
+        <v>0.1326</v>
       </c>
       <c r="J133" t="n">
-        <v>4.806</v>
+        <v>3.978</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>1.01</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0498</v>
+        <v>0.0375</v>
       </c>
       <c r="J134" t="n">
-        <v>1.494</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.98</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1105</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.315</v>
+        <v>-2.538</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.74</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7357</v>
+        <v>-0.7063</v>
       </c>
       <c r="J136" t="n">
-        <v>-22.071</v>
+        <v>-21.189</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.37</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6929</v>
+        <v>0.6351</v>
       </c>
       <c r="J137" t="n">
-        <v>20.787</v>
+        <v>19.053</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1645</v>
+        <v>0.1294</v>
       </c>
       <c r="J138" t="n">
-        <v>4.935</v>
+        <v>3.882</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0026</v>
+        <v>-0.0015</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.078</v>
+        <v>-0.045</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.96</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0759</v>
+        <v>-0.0608</v>
       </c>
       <c r="J140" t="n">
-        <v>-2.277</v>
+        <v>-1.824</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.83</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2261</v>
+        <v>-0.2057</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.783</v>
+        <v>-6.171</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.52</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7884</v>
+        <v>0.8731</v>
       </c>
       <c r="J142" t="n">
-        <v>17.3448</v>
+        <v>19.2082</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.73</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.3036</v>
+        <v>-0.2862</v>
       </c>
       <c r="J143" t="n">
-        <v>-6.6792</v>
+        <v>-6.2964</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.71</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3223</v>
+        <v>-0.3056</v>
       </c>
       <c r="J144" t="n">
-        <v>-7.0906</v>
+        <v>-6.7232</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.66</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3681</v>
+        <v>-0.3541</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.0982</v>
+        <v>-7.7902</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4571</v>
+        <v>-0.4514</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.0562</v>
+        <v>-9.9308</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.6</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7153</v>
+        <v>0.6431</v>
       </c>
       <c r="J147" t="n">
-        <v>15.7366</v>
+        <v>14.1482</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4614</v>
+        <v>0.3965</v>
       </c>
       <c r="J148" t="n">
-        <v>10.1508</v>
+        <v>8.723000000000001</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.24</v>
       </c>
       <c r="I149" t="n">
-        <v>0.342</v>
+        <v>0.2867</v>
       </c>
       <c r="J149" t="n">
-        <v>7.524</v>
+        <v>6.3074</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.22</v>
       </c>
       <c r="I150" t="n">
-        <v>0.319</v>
+        <v>0.2659</v>
       </c>
       <c r="J150" t="n">
-        <v>7.018</v>
+        <v>5.8498</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.89</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.179</v>
+        <v>-0.16</v>
       </c>
       <c r="J151" t="n">
-        <v>-3.938</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.35</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9034</v>
+        <v>0.8871</v>
       </c>
       <c r="J152" t="n">
-        <v>26.1986</v>
+        <v>25.7259</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.16</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4854</v>
+        <v>0.4434</v>
       </c>
       <c r="J153" t="n">
-        <v>14.0766</v>
+        <v>12.8586</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4614</v>
+        <v>0.4191</v>
       </c>
       <c r="J154" t="n">
-        <v>13.3806</v>
+        <v>12.1539</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.87</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4251</v>
+        <v>-0.382</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.3279</v>
+        <v>-11.078</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.0023</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="J156" t="n">
-        <v>-29.0667</v>
+        <v>-28.9855</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.51</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9165</v>
+        <v>0.8744</v>
       </c>
       <c r="J157" t="n">
-        <v>26.5785</v>
+        <v>25.3576</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.23</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4867</v>
+        <v>0.428</v>
       </c>
       <c r="J158" t="n">
-        <v>14.1143</v>
+        <v>12.412</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>1.16</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3663</v>
+        <v>0.3115</v>
       </c>
       <c r="J159" t="n">
-        <v>10.6227</v>
+        <v>9.0335</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>0.63</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.41</v>
+        <v>-0.4007</v>
       </c>
       <c r="J160" t="n">
-        <v>-11.89</v>
+        <v>-11.6203</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.42</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5888</v>
+        <v>-0.6041</v>
       </c>
       <c r="J161" t="n">
-        <v>-17.0752</v>
+        <v>-17.5189</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.45</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5621</v>
+        <v>0.4927</v>
       </c>
       <c r="J162" t="n">
-        <v>12.9283</v>
+        <v>11.3321</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.31</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4164</v>
+        <v>0.3555</v>
       </c>
       <c r="J163" t="n">
-        <v>9.577199999999999</v>
+        <v>8.176500000000001</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.27</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3737</v>
+        <v>0.3162</v>
       </c>
       <c r="J164" t="n">
-        <v>8.5951</v>
+        <v>7.2726</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.22</v>
       </c>
       <c r="I165" t="n">
-        <v>0.3168</v>
+        <v>0.2646</v>
       </c>
       <c r="J165" t="n">
-        <v>7.2864</v>
+        <v>6.0858</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>1.2</v>
       </c>
       <c r="I166" t="n">
-        <v>0.293</v>
+        <v>0.2431</v>
       </c>
       <c r="J166" t="n">
-        <v>6.739</v>
+        <v>5.5913</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>0.85</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.1725</v>
+        <v>-0.1569</v>
       </c>
       <c r="J167" t="n">
-        <v>-3.9675</v>
+        <v>-3.6087</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>0.79</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2354</v>
+        <v>-0.2204</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.4142</v>
+        <v>-5.0692</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.75</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2742</v>
+        <v>-0.2595</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.3066</v>
+        <v>-5.9685</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3277</v>
+        <v>-0.3135</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.5371</v>
+        <v>-7.2105</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.51</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4875</v>
+        <v>-0.4844</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.2125</v>
+        <v>-11.1412</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.3</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5898</v>
+        <v>0.5303</v>
       </c>
       <c r="J172" t="n">
-        <v>15.9246</v>
+        <v>14.3181</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.24</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4939</v>
+        <v>0.4348</v>
       </c>
       <c r="J173" t="n">
-        <v>13.3353</v>
+        <v>11.7396</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>1.13</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3044</v>
+        <v>0.2539</v>
       </c>
       <c r="J174" t="n">
-        <v>8.2188</v>
+        <v>6.8553</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1718</v>
+        <v>-0.1513</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.6386</v>
+        <v>-4.0851</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.59</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4481</v>
+        <v>-0.4435</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.0987</v>
+        <v>-11.9745</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.43</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0408</v>
+        <v>1.0468</v>
       </c>
       <c r="J177" t="n">
-        <v>28.1016</v>
+        <v>28.2636</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0248</v>
+        <v>1.0279</v>
       </c>
       <c r="J178" t="n">
-        <v>27.6696</v>
+        <v>27.7533</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.86</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.4549</v>
+        <v>-0.4121</v>
       </c>
       <c r="J179" t="n">
-        <v>-12.2823</v>
+        <v>-11.1267</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.575</v>
+        <v>-0.5355</v>
       </c>
       <c r="J180" t="n">
-        <v>-15.525</v>
+        <v>-14.4585</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.74</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7329</v>
+        <v>-0.703</v>
       </c>
       <c r="J181" t="n">
-        <v>-19.7883</v>
+        <v>-18.981</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.18</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4444</v>
+        <v>0.3919</v>
       </c>
       <c r="J182" t="n">
-        <v>11.5544</v>
+        <v>10.1894</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>0.95</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0733</v>
+        <v>-0.0612</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.9058</v>
+        <v>-1.5912</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>0.91</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1236</v>
+        <v>-0.1082</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.2136</v>
+        <v>-2.8132</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>0.64</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3874</v>
+        <v>-0.3749</v>
       </c>
       <c r="J185" t="n">
-        <v>-10.0724</v>
+        <v>-9.747400000000001</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4583</v>
+        <v>-0.4529</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.9158</v>
+        <v>-11.7754</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.51</v>
       </c>
       <c r="I187" t="n">
-        <v>1.0975</v>
+        <v>1.1095</v>
       </c>
       <c r="J187" t="n">
-        <v>28.535</v>
+        <v>28.847</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.5</v>
       </c>
       <c r="I188" t="n">
-        <v>1.0841</v>
+        <v>1.0951</v>
       </c>
       <c r="J188" t="n">
-        <v>28.1866</v>
+        <v>28.4726</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>1.23</v>
       </c>
       <c r="I189" t="n">
-        <v>0.5962</v>
+        <v>0.5682</v>
       </c>
       <c r="J189" t="n">
-        <v>15.5012</v>
+        <v>14.7732</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.5313</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="J190" t="n">
-        <v>13.8138</v>
+        <v>13.039</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>1.1</v>
       </c>
       <c r="I191" t="n">
-        <v>0.2926</v>
+        <v>0.2611</v>
       </c>
       <c r="J191" t="n">
-        <v>7.6076</v>
+        <v>6.7886</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.16</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4242</v>
+        <v>0.3754</v>
       </c>
       <c r="J192" t="n">
-        <v>10.605</v>
+        <v>9.385</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>0.9</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1301</v>
+        <v>-0.115</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.2525</v>
+        <v>-2.875</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>0.87</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1639</v>
+        <v>-0.1477</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.0975</v>
+        <v>-3.6925</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.6</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4186</v>
+        <v>-0.4087</v>
       </c>
       <c r="J195" t="n">
-        <v>-10.465</v>
+        <v>-10.2175</v>
       </c>
     </row>
     <row r="196">
@@ -10275,10 +10275,10 @@
         <v>1.69</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3428</v>
+        <v>1.3649</v>
       </c>
       <c r="J197" t="n">
-        <v>33.57</v>
+        <v>34.1225</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.47</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0505</v>
+        <v>1.0567</v>
       </c>
       <c r="J198" t="n">
-        <v>26.2625</v>
+        <v>26.4175</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>1.2</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5383</v>
+        <v>0.507</v>
       </c>
       <c r="J199" t="n">
-        <v>13.4575</v>
+        <v>12.675</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>1.03</v>
       </c>
       <c r="I200" t="n">
-        <v>0.0939</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J200" t="n">
-        <v>2.3475</v>
+        <v>1.835</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3634</v>
+        <v>-0.324</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.085000000000001</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1.56</v>
       </c>
       <c r="I202" t="n">
-        <v>1.0641</v>
+        <v>1.0735</v>
       </c>
       <c r="J202" t="n">
-        <v>25.5384</v>
+        <v>25.764</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.78</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2537</v>
+        <v>-0.2358</v>
       </c>
       <c r="J203" t="n">
-        <v>-6.0888</v>
+        <v>-5.6592</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.59</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.4277</v>
+        <v>-0.4187</v>
       </c>
       <c r="J204" t="n">
-        <v>-10.2648</v>
+        <v>-10.0488</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.57</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4454</v>
+        <v>-0.4381</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.6896</v>
+        <v>-10.5144</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.54</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4717</v>
+        <v>-0.4673</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.3208</v>
+        <v>-11.2152</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.85</v>
       </c>
       <c r="I207" t="n">
-        <v>1.5424</v>
+        <v>1.5798</v>
       </c>
       <c r="J207" t="n">
-        <v>37.0176</v>
+        <v>37.9152</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.29</v>
       </c>
       <c r="I208" t="n">
-        <v>0.7221</v>
+        <v>0.6969</v>
       </c>
       <c r="J208" t="n">
-        <v>17.3304</v>
+        <v>16.7256</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>1.2</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5369</v>
+        <v>0.5059</v>
       </c>
       <c r="J209" t="n">
-        <v>12.8856</v>
+        <v>12.1416</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>1.11</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3247</v>
+        <v>0.2926</v>
       </c>
       <c r="J210" t="n">
-        <v>7.7928</v>
+        <v>7.0224</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.9</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3919</v>
+        <v>-0.3527</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.4056</v>
+        <v>-8.4648</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.38</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9741</v>
+        <v>0.9701</v>
       </c>
       <c r="J212" t="n">
-        <v>26.3007</v>
+        <v>26.1927</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>1.13</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4199</v>
+        <v>0.3769</v>
       </c>
       <c r="J213" t="n">
-        <v>11.3373</v>
+        <v>10.1763</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2591</v>
+        <v>-0.2207</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.9957</v>
+        <v>-5.9589</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.78</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.6328</v>
+        <v>-0.5955</v>
       </c>
       <c r="J215" t="n">
-        <v>-17.0856</v>
+        <v>-16.0785</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.77</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6553</v>
+        <v>-0.6193</v>
       </c>
       <c r="J216" t="n">
-        <v>-17.6931</v>
+        <v>-16.7211</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.75</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1685</v>
+        <v>1.1605</v>
       </c>
       <c r="J217" t="n">
-        <v>31.5495</v>
+        <v>31.3335</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>0.98</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0461</v>
+        <v>-0.0348</v>
       </c>
       <c r="J218" t="n">
-        <v>-1.2447</v>
+        <v>-0.9396</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>0.95</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.4273</v>
+        <v>-1.9818</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>0.86</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1951</v>
+        <v>-0.1745</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.2677</v>
+        <v>-4.7115</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3518</v>
+        <v>-0.3377</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.4986</v>
+        <v>-9.117900000000001</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.8</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4278</v>
+        <v>1.4556</v>
       </c>
       <c r="J222" t="n">
-        <v>27.1282</v>
+        <v>27.6564</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>1.78</v>
       </c>
       <c r="I223" t="n">
-        <v>1.4039</v>
+        <v>1.4305</v>
       </c>
       <c r="J223" t="n">
-        <v>26.6741</v>
+        <v>27.1795</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>1.67</v>
       </c>
       <c r="I224" t="n">
-        <v>1.271</v>
+        <v>1.2925</v>
       </c>
       <c r="J224" t="n">
-        <v>24.149</v>
+        <v>24.5575</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>1.44</v>
       </c>
       <c r="I225" t="n">
-        <v>0.9721</v>
+        <v>0.9776</v>
       </c>
       <c r="J225" t="n">
-        <v>18.4699</v>
+        <v>18.5744</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.97</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2219</v>
+        <v>-0.1986</v>
       </c>
       <c r="J226" t="n">
-        <v>-4.2161</v>
+        <v>-3.7734</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>0.97</v>
       </c>
       <c r="I227" t="n">
-        <v>0.0519</v>
+        <v>0.0968</v>
       </c>
       <c r="J227" t="n">
-        <v>0.9861</v>
+        <v>1.8392</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>0.52</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.4584</v>
+        <v>-0.4538</v>
       </c>
       <c r="J228" t="n">
-        <v>-8.7096</v>
+        <v>-8.622199999999999</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>0.49</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.4846</v>
+        <v>-0.4818</v>
       </c>
       <c r="J229" t="n">
-        <v>-9.2074</v>
+        <v>-9.154199999999999</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.44</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5286</v>
+        <v>-0.53</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.0434</v>
+        <v>-10.07</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.44</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5286</v>
+        <v>-0.53</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.0434</v>
+        <v>-10.07</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>1.47</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1095</v>
+        <v>1.1254</v>
       </c>
       <c r="J232" t="n">
-        <v>31.066</v>
+        <v>31.5112</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>1.08</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2826</v>
+        <v>0.2437</v>
       </c>
       <c r="J233" t="n">
-        <v>7.9128</v>
+        <v>6.8236</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>1.06</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2259</v>
+        <v>0.1904</v>
       </c>
       <c r="J234" t="n">
-        <v>6.3252</v>
+        <v>5.3312</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>0.77</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.6607</v>
+        <v>-0.6254</v>
       </c>
       <c r="J235" t="n">
-        <v>-18.4996</v>
+        <v>-17.5112</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.74</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.6965</v>
       </c>
       <c r="J236" t="n">
-        <v>-20.3644</v>
+        <v>-19.502</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.24</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4948</v>
+        <v>0.4357</v>
       </c>
       <c r="J237" t="n">
-        <v>13.8544</v>
+        <v>12.1996</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.17</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3768</v>
+        <v>0.3216</v>
       </c>
       <c r="J238" t="n">
-        <v>10.5504</v>
+        <v>9.004799999999999</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>1.06</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1668</v>
+        <v>0.1307</v>
       </c>
       <c r="J239" t="n">
-        <v>4.6704</v>
+        <v>3.6596</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>0.87</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1823</v>
+        <v>-0.1617</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.1044</v>
+        <v>-4.5276</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.78</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2742</v>
+        <v>-0.2552</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.6776</v>
+        <v>-7.1456</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>2.06</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7754</v>
+        <v>1.8345</v>
       </c>
       <c r="J242" t="n">
-        <v>39.0588</v>
+        <v>40.359</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.44</v>
       </c>
       <c r="I243" t="n">
-        <v>0.9906</v>
+        <v>0.9902</v>
       </c>
       <c r="J243" t="n">
-        <v>21.7932</v>
+        <v>21.7844</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>1.18</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4808</v>
+        <v>0.4505</v>
       </c>
       <c r="J244" t="n">
-        <v>10.5776</v>
+        <v>9.911</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>1.09</v>
       </c>
       <c r="I245" t="n">
-        <v>0.26</v>
+        <v>0.2289</v>
       </c>
       <c r="J245" t="n">
-        <v>5.72</v>
+        <v>5.0358</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.96</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2295</v>
+        <v>-0.198</v>
       </c>
       <c r="J246" t="n">
-        <v>-5.049</v>
+        <v>-4.356</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>0.86</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1587</v>
+        <v>-0.1429</v>
       </c>
       <c r="J247" t="n">
-        <v>-3.4914</v>
+        <v>-3.1438</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>0.82</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2023</v>
+        <v>-0.187</v>
       </c>
       <c r="J248" t="n">
-        <v>-4.4506</v>
+        <v>-4.114</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.75</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2725</v>
+        <v>-0.2582</v>
       </c>
       <c r="J249" t="n">
-        <v>-5.995</v>
+        <v>-5.6804</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.61</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3974</v>
+        <v>-0.3864</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.742800000000001</v>
+        <v>-8.5008</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.48</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.512</v>
+        <v>-0.5118</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.264</v>
+        <v>-11.2596</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.6</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2237</v>
+        <v>1.2394</v>
       </c>
       <c r="J252" t="n">
-        <v>28.1451</v>
+        <v>28.5062</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.45</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0187</v>
+        <v>1.0202</v>
       </c>
       <c r="J253" t="n">
-        <v>23.4301</v>
+        <v>23.4646</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>1.2</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5369</v>
+        <v>0.5059</v>
       </c>
       <c r="J254" t="n">
-        <v>12.3487</v>
+        <v>11.6357</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>1.18</v>
       </c>
       <c r="I255" t="n">
-        <v>0.4924</v>
+        <v>0.4606</v>
       </c>
       <c r="J255" t="n">
-        <v>11.3252</v>
+        <v>10.5938</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.92</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3374</v>
+        <v>-0.2988</v>
       </c>
       <c r="J256" t="n">
-        <v>-7.7602</v>
+        <v>-6.8724</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.21</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5371</v>
+        <v>0.4949</v>
       </c>
       <c r="J257" t="n">
-        <v>12.3533</v>
+        <v>11.3827</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>0.8</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2313</v>
+        <v>-0.2151</v>
       </c>
       <c r="J258" t="n">
-        <v>-5.3199</v>
+        <v>-4.9473</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>0.67</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3509</v>
+        <v>-0.3364</v>
       </c>
       <c r="J259" t="n">
-        <v>-8.0707</v>
+        <v>-7.7372</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.67</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3509</v>
+        <v>-0.3364</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.0707</v>
+        <v>-7.7372</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.47</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.5301</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.1371</v>
+        <v>-12.1923</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.14</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3305</v>
+        <v>0.2778</v>
       </c>
       <c r="J262" t="n">
-        <v>9.914999999999999</v>
+        <v>8.334</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.07</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1936</v>
+        <v>0.1532</v>
       </c>
       <c r="J263" t="n">
-        <v>5.808</v>
+        <v>4.596</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.02</v>
       </c>
       <c r="I264" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0533</v>
       </c>
       <c r="J264" t="n">
-        <v>2.244</v>
+        <v>1.599</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.97</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0574</v>
+        <v>-0.0452</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.722</v>
+        <v>-1.356</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.74</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3093</v>
+        <v>-0.2919</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.279</v>
+        <v>-8.757</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.21</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6012</v>
+        <v>0.5624</v>
       </c>
       <c r="J267" t="n">
-        <v>18.036</v>
+        <v>16.872</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5554</v>
+        <v>0.5149</v>
       </c>
       <c r="J268" t="n">
-        <v>16.662</v>
+        <v>15.447</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.98</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1042</v>
+        <v>-0.0796</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.126</v>
+        <v>-2.388</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.97</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1405</v>
+        <v>-0.1112</v>
       </c>
       <c r="J270" t="n">
-        <v>-4.215</v>
+        <v>-3.336</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.8</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5937</v>
+        <v>-0.5548</v>
       </c>
       <c r="J271" t="n">
-        <v>-17.811</v>
+        <v>-16.644</v>
       </c>
     </row>
   </sheetData>
